--- a/input_folder/output/03_04-06-2017_template.xlsx
+++ b/input_folder/output/03_04-06-2017_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dozer" sheetId="1" state="visible" r:id="rId1"/>
@@ -322,6 +322,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -338,17 +349,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -478,28 +478,10 @@
     <xf numFmtId="9" fontId="3" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -517,16 +499,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -965,7 +965,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="108.95" customHeight="1">
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">Construction Management Institute 
 Addis Ababa University - Construction Productivity Research Group </t>
@@ -973,21 +973,21 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> PREPARATION OF NATIONAL PRODUCTIVITY NORM FOR WATER CONSTRUCTION TRADE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Dozer Productivity Data Collection Form </t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>Form - 1</t>
         </is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="K6" s="46" t="inlineStr">
+      <c r="K6" s="55" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
@@ -1017,6 +1017,11 @@
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Data Collector</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="27" customHeight="1"/>
     <row r="8" ht="15" customHeight="1" thickBot="1">
@@ -1141,22 +1146,35 @@
       <c r="R10" s="60" t="n"/>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 1</t>
-        </is>
+      <c r="B11" s="7" t="n">
+        <v>201</v>
       </c>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
+      <c r="L11" s="7">
+        <f>H11*I11*J11</f>
+        <v/>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>64</v>
+      </c>
       <c r="N11" s="7">
         <f>L11*3600/M11*0.764555</f>
         <v/>
@@ -1179,22 +1197,35 @@
       </c>
     </row>
     <row r="12" ht="33" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 2</t>
-        </is>
+      <c r="B12" s="8" t="n">
+        <v>202</v>
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
+      <c r="L12" s="8">
+        <f>H12*I12*J12</f>
+        <v/>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="N12" s="8">
         <f>L12*3600/M12*0.764555</f>
         <v/>
@@ -1205,22 +1236,35 @@
       <c r="R12" s="8" t="n"/>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 3</t>
-        </is>
+      <c r="B13" s="8" t="n">
+        <v>203</v>
       </c>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
+      <c r="L13" s="8">
+        <f>H13*I13*J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>81</v>
+      </c>
       <c r="N13" s="8">
         <f>L13*3600/M13*0.764555</f>
         <v/>
@@ -1231,22 +1275,35 @@
       <c r="R13" s="8" t="n"/>
     </row>
     <row r="14" ht="33" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 4</t>
-        </is>
+      <c r="B14" s="8" t="n">
+        <v>204</v>
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
+      <c r="L14" s="8">
+        <f>H14*I14*J14</f>
+        <v/>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>82</v>
+      </c>
       <c r="N14" s="8">
         <f>L14*3600/M14*0.764555</f>
         <v/>
@@ -1257,22 +1314,35 @@
       <c r="R14" s="8" t="n"/>
     </row>
     <row r="15" ht="33" customHeight="1" thickBot="1">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 5</t>
-        </is>
+      <c r="B15" s="9" t="n">
+        <v>205</v>
       </c>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
+      <c r="L15" s="8">
+        <f>H15*I15*J15</f>
+        <v/>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>119</v>
+      </c>
       <c r="N15" s="9">
         <f>L15*3600/M15*0.764555</f>
         <v/>
@@ -1283,22 +1353,35 @@
       <c r="R15" s="9" t="n"/>
     </row>
     <row r="16" ht="33" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 6</t>
-        </is>
+      <c r="B16" s="7" t="n">
+        <v>206</v>
       </c>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
+      <c r="L16" s="7">
+        <f>H16*I16*J16</f>
+        <v/>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>83</v>
+      </c>
       <c r="N16" s="7">
         <f>L16*3600/M16*0.764555</f>
         <v/>
@@ -1309,22 +1392,35 @@
       <c r="R16" s="7" t="n"/>
     </row>
     <row r="17" ht="33" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 7</t>
-        </is>
+      <c r="B17" s="8" t="n">
+        <v>207</v>
       </c>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
+      <c r="L17" s="8">
+        <f>H17*I17*J17</f>
+        <v/>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>84</v>
+      </c>
       <c r="N17" s="8">
         <f>L17*3600/M17*0.764555</f>
         <v/>
@@ -1335,22 +1431,35 @@
       <c r="R17" s="8" t="n"/>
     </row>
     <row r="18" ht="33" customHeight="1">
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 8</t>
-        </is>
+      <c r="B18" s="8" t="n">
+        <v>208</v>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
+      <c r="L18" s="8">
+        <f>H18*I18*J18</f>
+        <v/>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>87</v>
+      </c>
       <c r="N18" s="8">
         <f>L18*3600/M18*0.764555</f>
         <v/>
@@ -1361,22 +1470,35 @@
       <c r="R18" s="8" t="n"/>
     </row>
     <row r="19" ht="33" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 9</t>
-        </is>
+      <c r="B19" s="8" t="n">
+        <v>209</v>
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
+      <c r="L19" s="8">
+        <f>H19*I19*J19</f>
+        <v/>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>86</v>
+      </c>
       <c r="N19" s="8">
         <f>L19*3600/M19*0.764555</f>
         <v/>
@@ -1387,22 +1509,35 @@
       <c r="R19" s="8" t="n"/>
     </row>
     <row r="20" ht="33" customHeight="1" thickBot="1">
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 10</t>
-        </is>
+      <c r="B20" s="9" t="n">
+        <v>210</v>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
+      <c r="L20" s="8">
+        <f>H20*I20*J20</f>
+        <v/>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>91</v>
+      </c>
       <c r="N20" s="9">
         <f>L20*3600/M20*0.764555</f>
         <v/>
@@ -1413,1987 +1548,3157 @@
       <c r="R20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 11</t>
-        </is>
+      <c r="B21" s="7" t="n">
+        <v>211</v>
       </c>
       <c r="C21" s="7" t="n"/>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
+      <c r="L21" s="7">
+        <f>H21*I21*J21</f>
+        <v/>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>97</v>
+      </c>
       <c r="N21" s="7">
         <f>L21*3600/M21*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 12</t>
-        </is>
+      <c r="B22" s="8" t="n">
+        <v>212</v>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
+      <c r="L22" s="8">
+        <f>H22*I22*J22</f>
+        <v/>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>103</v>
+      </c>
       <c r="N22" s="8">
         <f>L22*3600/M22*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 13</t>
-        </is>
+      <c r="B23" s="8" t="n">
+        <v>213</v>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
+      <c r="L23" s="8">
+        <f>H23*I23*J23</f>
+        <v/>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>57</v>
+      </c>
       <c r="N23" s="8">
         <f>L23*3600/M23*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 14</t>
-        </is>
+      <c r="B24" s="8" t="n">
+        <v>214</v>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
+      <c r="L24" s="8">
+        <f>H24*I24*J24</f>
+        <v/>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>56</v>
+      </c>
       <c r="N24" s="8">
         <f>L24*3600/M24*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 15</t>
-        </is>
+      <c r="B25" s="9" t="n">
+        <v>215</v>
       </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
+      <c r="L25" s="8">
+        <f>H25*I25*J25</f>
+        <v/>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>37</v>
+      </c>
       <c r="N25" s="9">
         <f>L25*3600/M25*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 16</t>
-        </is>
+      <c r="B26" s="7" t="n">
+        <v>216</v>
       </c>
       <c r="C26" s="7" t="n"/>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
+      <c r="L26" s="7">
+        <f>H26*I26*J26</f>
+        <v/>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>63</v>
+      </c>
       <c r="N26" s="7">
         <f>L26*3600/M26*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 17</t>
-        </is>
+      <c r="B27" s="8" t="n">
+        <v>217</v>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="n"/>
       <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
+      <c r="L27" s="8">
+        <f>H27*I27*J27</f>
+        <v/>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="N27" s="8">
         <f>L27*3600/M27*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 18</t>
-        </is>
+      <c r="B28" s="8" t="n">
+        <v>218</v>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
+      <c r="L28" s="8">
+        <f>H28*I28*J28</f>
+        <v/>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="N28" s="8">
         <f>L28*3600/M28*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 19</t>
-        </is>
+      <c r="B29" s="8" t="n">
+        <v>219</v>
       </c>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
+      <c r="L29" s="8">
+        <f>H29*I29*J29</f>
+        <v/>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>63</v>
+      </c>
       <c r="N29" s="8">
         <f>L29*3600/M29*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 20</t>
-        </is>
+      <c r="B30" s="9" t="n">
+        <v>220</v>
       </c>
       <c r="C30" s="9" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
+      <c r="L30" s="8">
+        <f>H30*I30*J30</f>
+        <v/>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>64</v>
+      </c>
       <c r="N30" s="9">
         <f>L30*3600/M30*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 21</t>
-        </is>
+      <c r="B31" s="7" t="n">
+        <v>221</v>
       </c>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
+      <c r="L31" s="7">
+        <f>H31*I31*J31</f>
+        <v/>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>76</v>
+      </c>
       <c r="N31" s="7">
         <f>L31*3600/M31*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 22</t>
-        </is>
+      <c r="B32" s="8" t="n">
+        <v>222</v>
       </c>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
       <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
+      <c r="L32" s="8">
+        <f>H32*I32*J32</f>
+        <v/>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>51</v>
+      </c>
       <c r="N32" s="8">
         <f>L32*3600/M32*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 23</t>
-        </is>
+      <c r="B33" s="8" t="n">
+        <v>223</v>
       </c>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="n"/>
       <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
+      <c r="L33" s="8">
+        <f>H33*I33*J33</f>
+        <v/>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>57</v>
+      </c>
       <c r="N33" s="8">
         <f>L33*3600/M33*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 24</t>
-        </is>
+      <c r="B34" s="8" t="n">
+        <v>224</v>
       </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="n"/>
       <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="n"/>
+      <c r="L34" s="8">
+        <f>H34*I34*J34</f>
+        <v/>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>92</v>
+      </c>
       <c r="N34" s="8">
         <f>L34*3600/M34*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 25</t>
-        </is>
+      <c r="B35" s="9" t="n">
+        <v>225</v>
       </c>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
+      <c r="L35" s="8">
+        <f>H35*I35*J35</f>
+        <v/>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>96</v>
+      </c>
       <c r="N35" s="9">
         <f>L35*3600/M35*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 26</t>
-        </is>
+      <c r="B36" s="7" t="n">
+        <v>226</v>
       </c>
       <c r="C36" s="7" t="n"/>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
       <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
+      <c r="L36" s="7">
+        <f>H36*I36*J36</f>
+        <v/>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>41</v>
+      </c>
       <c r="N36" s="7">
         <f>L36*3600/M36*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 27</t>
-        </is>
+      <c r="B37" s="8" t="n">
+        <v>227</v>
       </c>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
+      <c r="L37" s="8">
+        <f>H37*I37*J37</f>
+        <v/>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>74</v>
+      </c>
       <c r="N37" s="8">
         <f>L37*3600/M37*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 28</t>
-        </is>
+      <c r="B38" s="8" t="n">
+        <v>228</v>
       </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="n"/>
       <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
+      <c r="L38" s="8">
+        <f>H38*I38*J38</f>
+        <v/>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>37</v>
+      </c>
       <c r="N38" s="8">
         <f>L38*3600/M38*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 29</t>
-        </is>
+      <c r="B39" s="8" t="n">
+        <v>229</v>
       </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K39" s="8" t="n"/>
-      <c r="L39" s="8" t="n"/>
-      <c r="M39" s="8" t="n"/>
+      <c r="L39" s="8">
+        <f>H39*I39*J39</f>
+        <v/>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>81</v>
+      </c>
       <c r="N39" s="8">
         <f>L39*3600/M39*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 30</t>
-        </is>
+      <c r="B40" s="9" t="n">
+        <v>230</v>
       </c>
       <c r="C40" s="9" t="n"/>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="9" t="n"/>
+      <c r="L40" s="8">
+        <f>H40*I40*J40</f>
+        <v/>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>36</v>
+      </c>
       <c r="N40" s="9">
         <f>L40*3600/M40*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 31</t>
-        </is>
+      <c r="B41" s="7" t="n">
+        <v>231</v>
       </c>
       <c r="C41" s="7" t="n"/>
       <c r="D41" s="7" t="n"/>
       <c r="E41" s="7" t="n"/>
       <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
+      <c r="L41" s="7">
+        <f>H41*I41*J41</f>
+        <v/>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>62</v>
+      </c>
       <c r="N41" s="7">
         <f>L41*3600/M41*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 32</t>
-        </is>
+      <c r="B42" s="8" t="n">
+        <v>232</v>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K42" s="8" t="n"/>
-      <c r="L42" s="8" t="n"/>
-      <c r="M42" s="8" t="n"/>
+      <c r="L42" s="8">
+        <f>H42*I42*J42</f>
+        <v/>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>64</v>
+      </c>
       <c r="N42" s="8">
         <f>L42*3600/M42*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 33</t>
-        </is>
+      <c r="B43" s="8" t="n">
+        <v>233</v>
       </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K43" s="8" t="n"/>
-      <c r="L43" s="8" t="n"/>
-      <c r="M43" s="8" t="n"/>
+      <c r="L43" s="8">
+        <f>H43*I43*J43</f>
+        <v/>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>67</v>
+      </c>
       <c r="N43" s="8">
         <f>L43*3600/M43*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 34</t>
-        </is>
+      <c r="B44" s="8" t="n">
+        <v>234</v>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K44" s="8" t="n"/>
-      <c r="L44" s="8" t="n"/>
-      <c r="M44" s="8" t="n"/>
+      <c r="L44" s="8">
+        <f>H44*I44*J44</f>
+        <v/>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>72</v>
+      </c>
       <c r="N44" s="8">
         <f>L44*3600/M44*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 35</t>
-        </is>
+      <c r="B45" s="9" t="n">
+        <v>235</v>
       </c>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
+      <c r="L45" s="8">
+        <f>H45*I45*J45</f>
+        <v/>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>78</v>
+      </c>
       <c r="N45" s="9">
         <f>L45*3600/M45*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 36</t>
-        </is>
+      <c r="B46" s="7" t="n">
+        <v>236</v>
       </c>
       <c r="C46" s="7" t="n"/>
       <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n"/>
       <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
+      <c r="L46" s="7">
+        <f>H46*I46*J46</f>
+        <v/>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>76</v>
+      </c>
       <c r="N46" s="7">
         <f>L46*3600/M46*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 37</t>
-        </is>
+      <c r="B47" s="8" t="n">
+        <v>237</v>
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K47" s="8" t="n"/>
-      <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
+      <c r="L47" s="8">
+        <f>H47*I47*J47</f>
+        <v/>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>57</v>
+      </c>
       <c r="N47" s="8">
         <f>L47*3600/M47*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 38</t>
-        </is>
+      <c r="B48" s="8" t="n">
+        <v>238</v>
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="n"/>
       <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K48" s="8" t="n"/>
-      <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
+      <c r="L48" s="8">
+        <f>H48*I48*J48</f>
+        <v/>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="N48" s="8">
         <f>L48*3600/M48*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 39</t>
-        </is>
+      <c r="B49" s="8" t="n">
+        <v>239</v>
       </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
+      <c r="L49" s="8">
+        <f>H49*I49*J49</f>
+        <v/>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="N49" s="8">
         <f>L49*3600/M49*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 40</t>
-        </is>
+      <c r="B50" s="9" t="n">
+        <v>240</v>
       </c>
       <c r="C50" s="9" t="n"/>
       <c r="D50" s="9" t="n"/>
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
+      <c r="L50" s="8">
+        <f>H50*I50*J50</f>
+        <v/>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>96</v>
+      </c>
       <c r="N50" s="9">
         <f>L50*3600/M50*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 41</t>
-        </is>
+      <c r="B51" s="7" t="n">
+        <v>241</v>
       </c>
       <c r="C51" s="7" t="n"/>
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="L51" s="7">
+        <f>H51*I51*J51</f>
+        <v/>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>74</v>
+      </c>
       <c r="N51" s="7">
         <f>L51*3600/M51*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 42</t>
-        </is>
+      <c r="B52" s="8" t="n">
+        <v>242</v>
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="n"/>
       <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K52" s="8" t="n"/>
-      <c r="L52" s="8" t="n"/>
-      <c r="M52" s="8" t="n"/>
+      <c r="L52" s="8">
+        <f>H52*I52*J52</f>
+        <v/>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>73</v>
+      </c>
       <c r="N52" s="8">
         <f>L52*3600/M52*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 43</t>
-        </is>
+      <c r="B53" s="8" t="n">
+        <v>243</v>
       </c>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I53" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K53" s="8" t="n"/>
-      <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8" t="n"/>
+      <c r="L53" s="8">
+        <f>H53*I53*J53</f>
+        <v/>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>61</v>
+      </c>
       <c r="N53" s="8">
         <f>L53*3600/M53*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 44</t>
-        </is>
+      <c r="B54" s="8" t="n">
+        <v>244</v>
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="n"/>
       <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K54" s="8" t="n"/>
-      <c r="L54" s="8" t="n"/>
-      <c r="M54" s="8" t="n"/>
+      <c r="L54" s="8">
+        <f>H54*I54*J54</f>
+        <v/>
+      </c>
+      <c r="M54" s="8" t="n">
+        <v>67</v>
+      </c>
       <c r="N54" s="8">
         <f>L54*3600/M54*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 45</t>
-        </is>
+      <c r="B55" s="9" t="n">
+        <v>245</v>
       </c>
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="9" t="n"/>
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K55" s="9" t="n"/>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="9" t="n"/>
+      <c r="L55" s="8">
+        <f>H55*I55*J55</f>
+        <v/>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>58</v>
+      </c>
       <c r="N55" s="9">
         <f>L55*3600/M55*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 46</t>
-        </is>
+      <c r="B56" s="7" t="n">
+        <v>246</v>
       </c>
       <c r="C56" s="7" t="n"/>
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
-      <c r="J56" s="7" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K56" s="7" t="n"/>
-      <c r="L56" s="7" t="n"/>
-      <c r="M56" s="7" t="n"/>
+      <c r="L56" s="7">
+        <f>H56*I56*J56</f>
+        <v/>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>62</v>
+      </c>
       <c r="N56" s="7">
         <f>L56*3600/M56*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 47</t>
-        </is>
+      <c r="B57" s="8" t="n">
+        <v>247</v>
       </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K57" s="8" t="n"/>
-      <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="n"/>
+      <c r="L57" s="8">
+        <f>H57*I57*J57</f>
+        <v/>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>52</v>
+      </c>
       <c r="N57" s="8">
         <f>L57*3600/M57*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 48</t>
-        </is>
+      <c r="B58" s="8" t="n">
+        <v>248</v>
       </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K58" s="8" t="n"/>
-      <c r="L58" s="8" t="n"/>
-      <c r="M58" s="8" t="n"/>
+      <c r="L58" s="8">
+        <f>H58*I58*J58</f>
+        <v/>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>98</v>
+      </c>
       <c r="N58" s="8">
         <f>L58*3600/M58*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 49</t>
-        </is>
+      <c r="B59" s="8" t="n">
+        <v>249</v>
       </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="n"/>
       <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K59" s="8" t="n"/>
-      <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8" t="n"/>
+      <c r="L59" s="8">
+        <f>H59*I59*J59</f>
+        <v/>
+      </c>
+      <c r="M59" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="N59" s="8">
         <f>L59*3600/M59*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 50</t>
-        </is>
+      <c r="B60" s="9" t="n">
+        <v>250</v>
       </c>
       <c r="C60" s="9" t="n"/>
       <c r="D60" s="9" t="n"/>
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-      <c r="I60" s="9" t="n"/>
-      <c r="J60" s="9" t="n"/>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K60" s="9" t="n"/>
-      <c r="L60" s="9" t="n"/>
-      <c r="M60" s="9" t="n"/>
+      <c r="L60" s="8">
+        <f>H60*I60*J60</f>
+        <v/>
+      </c>
+      <c r="M60" s="9" t="n">
+        <v>96</v>
+      </c>
       <c r="N60" s="9">
         <f>L60*3600/M60*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 51</t>
-        </is>
+      <c r="B61" s="7" t="n">
+        <v>251</v>
       </c>
       <c r="C61" s="7" t="n"/>
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
+      <c r="L61" s="7">
+        <f>H61*I61*J61</f>
+        <v/>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>75</v>
+      </c>
       <c r="N61" s="7">
         <f>L61*3600/M61*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 52</t>
-        </is>
+      <c r="B62" s="8" t="n">
+        <v>252</v>
       </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="n"/>
       <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K62" s="8" t="n"/>
-      <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
+      <c r="L62" s="8">
+        <f>H62*I62*J62</f>
+        <v/>
+      </c>
+      <c r="M62" s="8" t="n">
+        <v>78</v>
+      </c>
       <c r="N62" s="8">
         <f>L62*3600/M62*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 53</t>
-        </is>
+      <c r="B63" s="8" t="n">
+        <v>253</v>
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K63" s="8" t="n"/>
-      <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8" t="n"/>
+      <c r="L63" s="8">
+        <f>H63*I63*J63</f>
+        <v/>
+      </c>
+      <c r="M63" s="8" t="n">
+        <v>76</v>
+      </c>
       <c r="N63" s="8">
         <f>L63*3600/M63*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 54</t>
-        </is>
+      <c r="B64" s="8" t="n">
+        <v>254</v>
       </c>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K64" s="8" t="n"/>
-      <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
+      <c r="L64" s="8">
+        <f>H64*I64*J64</f>
+        <v/>
+      </c>
+      <c r="M64" s="8" t="n">
+        <v>79</v>
+      </c>
       <c r="N64" s="8">
         <f>L64*3600/M64*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 55</t>
-        </is>
+      <c r="B65" s="9" t="n">
+        <v>255</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K65" s="9" t="n"/>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="9" t="n"/>
+      <c r="L65" s="8">
+        <f>H65*I65*J65</f>
+        <v/>
+      </c>
+      <c r="M65" s="9" t="n">
+        <v>74</v>
+      </c>
       <c r="N65" s="9">
         <f>L65*3600/M65*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 56</t>
-        </is>
+      <c r="B66" s="7" t="n">
+        <v>256</v>
       </c>
       <c r="C66" s="7" t="n"/>
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
+      <c r="L66" s="7">
+        <f>H66*I66*J66</f>
+        <v/>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>38</v>
+      </c>
       <c r="N66" s="7">
         <f>L66*3600/M66*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 57</t>
-        </is>
+      <c r="B67" s="8" t="n">
+        <v>257</v>
       </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="n"/>
       <c r="F67" s="8" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="8" t="n"/>
-      <c r="I67" s="8" t="n"/>
-      <c r="J67" s="8" t="n"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I67" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K67" s="8" t="n"/>
-      <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
+      <c r="L67" s="8">
+        <f>H67*I67*J67</f>
+        <v/>
+      </c>
+      <c r="M67" s="8" t="n">
+        <v>43</v>
+      </c>
       <c r="N67" s="8">
         <f>L67*3600/M67*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 58</t>
-        </is>
+      <c r="B68" s="8" t="n">
+        <v>258</v>
       </c>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="n"/>
       <c r="F68" s="8" t="n"/>
-      <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K68" s="8" t="n"/>
-      <c r="L68" s="8" t="n"/>
-      <c r="M68" s="8" t="n"/>
+      <c r="L68" s="8">
+        <f>H68*I68*J68</f>
+        <v/>
+      </c>
+      <c r="M68" s="8" t="n">
+        <v>57</v>
+      </c>
       <c r="N68" s="8">
         <f>L68*3600/M68*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 59</t>
-        </is>
+      <c r="B69" s="8" t="n">
+        <v>259</v>
       </c>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="n"/>
       <c r="F69" s="8" t="n"/>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="n"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
+      <c r="L69" s="8">
+        <f>H69*I69*J69</f>
+        <v/>
+      </c>
+      <c r="M69" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="N69" s="8">
         <f>L69*3600/M69*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 60</t>
-        </is>
+      <c r="B70" s="9" t="n">
+        <v>260</v>
       </c>
       <c r="C70" s="9" t="n"/>
       <c r="D70" s="9" t="n"/>
       <c r="E70" s="9" t="n"/>
       <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K70" s="9" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="9" t="n"/>
+      <c r="L70" s="8">
+        <f>H70*I70*J70</f>
+        <v/>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>78</v>
+      </c>
       <c r="N70" s="9">
         <f>L70*3600/M70*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 61</t>
-        </is>
+      <c r="B71" s="7" t="n">
+        <v>261</v>
       </c>
       <c r="C71" s="7" t="n"/>
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="7" t="n"/>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="7" t="n"/>
-      <c r="I71" s="7" t="n"/>
-      <c r="J71" s="7" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K71" s="7" t="n"/>
-      <c r="L71" s="7" t="n"/>
-      <c r="M71" s="7" t="n"/>
+      <c r="L71" s="7">
+        <f>H71*I71*J71</f>
+        <v/>
+      </c>
+      <c r="M71" s="7" t="n">
+        <v>61</v>
+      </c>
       <c r="N71" s="7">
         <f>L71*3600/M71*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 62</t>
-        </is>
+      <c r="B72" s="8" t="n">
+        <v>262</v>
       </c>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
       <c r="E72" s="8" t="n"/>
       <c r="F72" s="8" t="n"/>
-      <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="8" t="n"/>
-      <c r="J72" s="8" t="n"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K72" s="8" t="n"/>
-      <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="n"/>
+      <c r="L72" s="8">
+        <f>H72*I72*J72</f>
+        <v/>
+      </c>
+      <c r="M72" s="8" t="n">
+        <v>67</v>
+      </c>
       <c r="N72" s="8">
         <f>L72*3600/M72*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 63</t>
-        </is>
+      <c r="B73" s="8" t="n">
+        <v>263</v>
       </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
       <c r="E73" s="8" t="n"/>
       <c r="F73" s="8" t="n"/>
-      <c r="G73" s="8" t="n"/>
-      <c r="H73" s="8" t="n"/>
-      <c r="I73" s="8" t="n"/>
-      <c r="J73" s="8" t="n"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K73" s="8" t="n"/>
-      <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8" t="n"/>
+      <c r="L73" s="8">
+        <f>H73*I73*J73</f>
+        <v/>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>84</v>
+      </c>
       <c r="N73" s="8">
         <f>L73*3600/M73*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 64</t>
-        </is>
+      <c r="B74" s="8" t="n">
+        <v>264</v>
       </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="n"/>
       <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-      <c r="I74" s="8" t="n"/>
-      <c r="J74" s="8" t="n"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I74" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K74" s="8" t="n"/>
-      <c r="L74" s="8" t="n"/>
-      <c r="M74" s="8" t="n"/>
+      <c r="L74" s="8">
+        <f>H74*I74*J74</f>
+        <v/>
+      </c>
+      <c r="M74" s="8" t="n">
+        <v>88</v>
+      </c>
       <c r="N74" s="8">
         <f>L74*3600/M74*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 65</t>
-        </is>
+      <c r="B75" s="9" t="n">
+        <v>265</v>
       </c>
       <c r="C75" s="9" t="n"/>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
-      <c r="H75" s="9" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="9" t="n"/>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K75" s="9" t="n"/>
-      <c r="L75" s="9" t="n"/>
-      <c r="M75" s="9" t="n"/>
+      <c r="L75" s="8">
+        <f>H75*I75*J75</f>
+        <v/>
+      </c>
+      <c r="M75" s="9" t="n">
+        <v>67</v>
+      </c>
       <c r="N75" s="9">
         <f>L75*3600/M75*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 66</t>
-        </is>
+      <c r="B76" s="7" t="n">
+        <v>266</v>
       </c>
       <c r="C76" s="7" t="n"/>
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="7" t="n"/>
       <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K76" s="7" t="n"/>
-      <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
+      <c r="L76" s="7">
+        <f>H76*I76*J76</f>
+        <v/>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>96</v>
+      </c>
       <c r="N76" s="7">
         <f>L76*3600/M76*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 67</t>
-        </is>
+      <c r="B77" s="8" t="n">
+        <v>267</v>
       </c>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="8" t="n"/>
-      <c r="J77" s="8" t="n"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K77" s="8" t="n"/>
-      <c r="L77" s="8" t="n"/>
-      <c r="M77" s="8" t="n"/>
+      <c r="L77" s="8">
+        <f>H77*I77*J77</f>
+        <v/>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>109</v>
+      </c>
       <c r="N77" s="8">
         <f>L77*3600/M77*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 68</t>
-        </is>
+      <c r="B78" s="8" t="n">
+        <v>268</v>
       </c>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I78" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K78" s="8" t="n"/>
-      <c r="L78" s="8" t="n"/>
-      <c r="M78" s="8" t="n"/>
+      <c r="L78" s="8">
+        <f>H78*I78*J78</f>
+        <v/>
+      </c>
+      <c r="M78" s="8" t="n">
+        <v>112</v>
+      </c>
       <c r="N78" s="8">
         <f>L78*3600/M78*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 69</t>
-        </is>
+      <c r="B79" s="8" t="n">
+        <v>269</v>
       </c>
       <c r="C79" s="8" t="n"/>
       <c r="D79" s="8" t="n"/>
       <c r="E79" s="8" t="n"/>
       <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="8" t="n"/>
-      <c r="J79" s="8" t="n"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I79" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K79" s="8" t="n"/>
-      <c r="L79" s="8" t="n"/>
-      <c r="M79" s="8" t="n"/>
+      <c r="L79" s="8">
+        <f>H79*I79*J79</f>
+        <v/>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>107</v>
+      </c>
       <c r="N79" s="8">
         <f>L79*3600/M79*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 70</t>
-        </is>
+      <c r="B80" s="9" t="n">
+        <v>270</v>
       </c>
       <c r="C80" s="9" t="n"/>
       <c r="D80" s="9" t="n"/>
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
-      <c r="H80" s="9" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="9" t="n"/>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I80" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K80" s="9" t="n"/>
-      <c r="L80" s="9" t="n"/>
-      <c r="M80" s="9" t="n"/>
+      <c r="L80" s="8">
+        <f>H80*I80*J80</f>
+        <v/>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>108</v>
+      </c>
       <c r="N80" s="9">
         <f>L80*3600/M80*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 71</t>
-        </is>
+      <c r="B81" s="7" t="n">
+        <v>271</v>
       </c>
       <c r="C81" s="7" t="n"/>
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="7" t="n"/>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="n"/>
-      <c r="J81" s="7" t="n"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K81" s="7" t="n"/>
-      <c r="L81" s="7" t="n"/>
-      <c r="M81" s="7" t="n"/>
+      <c r="L81" s="7">
+        <f>H81*I81*J81</f>
+        <v/>
+      </c>
+      <c r="M81" s="7" t="n">
+        <v>23</v>
+      </c>
       <c r="N81" s="7">
         <f>L81*3600/M81*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 72</t>
-        </is>
+      <c r="B82" s="8" t="n">
+        <v>272</v>
       </c>
       <c r="C82" s="8" t="n"/>
       <c r="D82" s="8" t="n"/>
       <c r="E82" s="8" t="n"/>
       <c r="F82" s="8" t="n"/>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I82" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J82" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="n"/>
+      <c r="L82" s="8">
+        <f>H82*I82*J82</f>
+        <v/>
+      </c>
+      <c r="M82" s="8" t="n">
+        <v>28</v>
+      </c>
       <c r="N82" s="8">
         <f>L82*3600/M82*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 73</t>
-        </is>
+      <c r="B83" s="8" t="n">
+        <v>273</v>
       </c>
       <c r="C83" s="8" t="n"/>
       <c r="D83" s="8" t="n"/>
       <c r="E83" s="8" t="n"/>
       <c r="F83" s="8" t="n"/>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
-      <c r="I83" s="8" t="n"/>
-      <c r="J83" s="8" t="n"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K83" s="8" t="n"/>
-      <c r="L83" s="8" t="n"/>
-      <c r="M83" s="8" t="n"/>
+      <c r="L83" s="8">
+        <f>H83*I83*J83</f>
+        <v/>
+      </c>
+      <c r="M83" s="8" t="n">
+        <v>64</v>
+      </c>
       <c r="N83" s="8">
         <f>L83*3600/M83*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 74</t>
-        </is>
+      <c r="B84" s="8" t="n">
+        <v>274</v>
       </c>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-      <c r="I84" s="8" t="n"/>
-      <c r="J84" s="8" t="n"/>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I84" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J84" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K84" s="8" t="n"/>
-      <c r="L84" s="8" t="n"/>
-      <c r="M84" s="8" t="n"/>
+      <c r="L84" s="8">
+        <f>H84*I84*J84</f>
+        <v/>
+      </c>
+      <c r="M84" s="8" t="n">
+        <v>56</v>
+      </c>
       <c r="N84" s="8">
         <f>L84*3600/M84*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 75</t>
-        </is>
+      <c r="B85" s="9" t="n">
+        <v>275</v>
       </c>
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="9" t="n"/>
       <c r="E85" s="9" t="n"/>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="n"/>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I85" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K85" s="9" t="n"/>
-      <c r="L85" s="9" t="n"/>
-      <c r="M85" s="9" t="n"/>
+      <c r="L85" s="8">
+        <f>H85*I85*J85</f>
+        <v/>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="N85" s="9">
         <f>L85*3600/M85*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 76</t>
-        </is>
+      <c r="B86" s="7" t="n">
+        <v>276</v>
       </c>
       <c r="C86" s="7" t="n"/>
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K86" s="7" t="n"/>
-      <c r="L86" s="7" t="n"/>
-      <c r="M86" s="7" t="n"/>
+      <c r="L86" s="7">
+        <f>H86*I86*J86</f>
+        <v/>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>64</v>
+      </c>
       <c r="N86" s="7">
         <f>L86*3600/M86*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 77</t>
-        </is>
+      <c r="B87" s="8" t="n">
+        <v>277</v>
       </c>
       <c r="C87" s="8" t="n"/>
       <c r="D87" s="8" t="n"/>
       <c r="E87" s="8" t="n"/>
       <c r="F87" s="8" t="n"/>
-      <c r="G87" s="8" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="8" t="n"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I87" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J87" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K87" s="8" t="n"/>
-      <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8" t="n"/>
+      <c r="L87" s="8">
+        <f>H87*I87*J87</f>
+        <v/>
+      </c>
+      <c r="M87" s="8" t="n">
+        <v>87</v>
+      </c>
       <c r="N87" s="8">
         <f>L87*3600/M87*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 78</t>
-        </is>
+      <c r="B88" s="8" t="n">
+        <v>278</v>
       </c>
       <c r="C88" s="8" t="n"/>
       <c r="D88" s="8" t="n"/>
       <c r="E88" s="8" t="n"/>
       <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="8" t="n"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I88" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J88" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K88" s="8" t="n"/>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
+      <c r="L88" s="8">
+        <f>H88*I88*J88</f>
+        <v/>
+      </c>
+      <c r="M88" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="N88" s="8">
         <f>L88*3600/M88*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 79</t>
-        </is>
+      <c r="B89" s="8" t="n">
+        <v>279</v>
       </c>
       <c r="C89" s="8" t="n"/>
       <c r="D89" s="8" t="n"/>
       <c r="E89" s="8" t="n"/>
       <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-      <c r="I89" s="8" t="n"/>
-      <c r="J89" s="8" t="n"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I89" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J89" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K89" s="8" t="n"/>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
+      <c r="L89" s="8">
+        <f>H89*I89*J89</f>
+        <v/>
+      </c>
+      <c r="M89" s="8" t="n">
+        <v>98</v>
+      </c>
       <c r="N89" s="8">
         <f>L89*3600/M89*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 80</t>
-        </is>
+      <c r="B90" s="9" t="n">
+        <v>280</v>
       </c>
       <c r="C90" s="9" t="n"/>
       <c r="D90" s="9" t="n"/>
       <c r="E90" s="9" t="n"/>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
-      <c r="J90" s="9" t="n"/>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K90" s="9" t="n"/>
-      <c r="L90" s="9" t="n"/>
-      <c r="M90" s="9" t="n"/>
+      <c r="L90" s="8">
+        <f>H90*I90*J90</f>
+        <v/>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>87</v>
+      </c>
       <c r="N90" s="9">
         <f>L90*3600/M90*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 81</t>
-        </is>
+      <c r="B91" s="7" t="n">
+        <v>281</v>
       </c>
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K91" s="7" t="n"/>
-      <c r="L91" s="7" t="n"/>
-      <c r="M91" s="7" t="n"/>
+      <c r="L91" s="7">
+        <f>H91*I91*J91</f>
+        <v/>
+      </c>
+      <c r="M91" s="7" t="n">
+        <v>81</v>
+      </c>
       <c r="N91" s="7">
         <f>L91*3600/M91*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 82</t>
-        </is>
+      <c r="B92" s="8" t="n">
+        <v>282</v>
       </c>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
-      <c r="I92" s="8" t="n"/>
-      <c r="J92" s="8" t="n"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I92" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J92" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K92" s="8" t="n"/>
-      <c r="L92" s="8" t="n"/>
-      <c r="M92" s="8" t="n"/>
+      <c r="L92" s="8">
+        <f>H92*I92*J92</f>
+        <v/>
+      </c>
+      <c r="M92" s="8" t="n">
+        <v>83</v>
+      </c>
       <c r="N92" s="8">
         <f>L92*3600/M92*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 83</t>
-        </is>
+      <c r="B93" s="8" t="n">
+        <v>283</v>
       </c>
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="8" t="n"/>
       <c r="E93" s="8" t="n"/>
       <c r="F93" s="8" t="n"/>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
-      <c r="I93" s="8" t="n"/>
-      <c r="J93" s="8" t="n"/>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I93" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J93" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K93" s="8" t="n"/>
-      <c r="L93" s="8" t="n"/>
-      <c r="M93" s="8" t="n"/>
+      <c r="L93" s="8">
+        <f>H93*I93*J93</f>
+        <v/>
+      </c>
+      <c r="M93" s="8" t="n">
+        <v>61</v>
+      </c>
       <c r="N93" s="8">
         <f>L93*3600/M93*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 84</t>
-        </is>
+      <c r="B94" s="8" t="n">
+        <v>284</v>
       </c>
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="8" t="n"/>
       <c r="E94" s="8" t="n"/>
       <c r="F94" s="8" t="n"/>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="8" t="n"/>
-      <c r="J94" s="8" t="n"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I94" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J94" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K94" s="8" t="n"/>
-      <c r="L94" s="8" t="n"/>
-      <c r="M94" s="8" t="n"/>
+      <c r="L94" s="8">
+        <f>H94*I94*J94</f>
+        <v/>
+      </c>
+      <c r="M94" s="8" t="n">
+        <v>51</v>
+      </c>
       <c r="N94" s="8">
         <f>L94*3600/M94*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 85</t>
-        </is>
+      <c r="B95" s="9" t="n">
+        <v>285</v>
       </c>
       <c r="C95" s="9" t="n"/>
       <c r="D95" s="9" t="n"/>
       <c r="E95" s="9" t="n"/>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K95" s="9" t="n"/>
-      <c r="L95" s="9" t="n"/>
-      <c r="M95" s="9" t="n"/>
+      <c r="L95" s="8">
+        <f>H95*I95*J95</f>
+        <v/>
+      </c>
+      <c r="M95" s="9" t="n">
+        <v>43</v>
+      </c>
       <c r="N95" s="9">
         <f>L95*3600/M95*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 86</t>
-        </is>
+      <c r="B96" s="7" t="n">
+        <v>286</v>
       </c>
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K96" s="7" t="n"/>
-      <c r="L96" s="7" t="n"/>
-      <c r="M96" s="7" t="n"/>
+      <c r="L96" s="7">
+        <f>H96*I96*J96</f>
+        <v/>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>44</v>
+      </c>
       <c r="N96" s="7">
         <f>L96*3600/M96*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 87</t>
-        </is>
+      <c r="B97" s="8" t="n">
+        <v>287</v>
       </c>
       <c r="C97" s="8" t="n"/>
       <c r="D97" s="8" t="n"/>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8" t="n"/>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
-      <c r="J97" s="8" t="n"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J97" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
+      <c r="L97" s="8">
+        <f>H97*I97*J97</f>
+        <v/>
+      </c>
+      <c r="M97" s="8" t="n">
+        <v>57</v>
+      </c>
       <c r="N97" s="8">
         <f>L97*3600/M97*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 88</t>
-        </is>
+      <c r="B98" s="8" t="n">
+        <v>288</v>
       </c>
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I98" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J98" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K98" s="8" t="n"/>
-      <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
+      <c r="L98" s="8">
+        <f>H98*I98*J98</f>
+        <v/>
+      </c>
+      <c r="M98" s="8" t="n">
+        <v>61</v>
+      </c>
       <c r="N98" s="8">
         <f>L98*3600/M98*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 89</t>
-        </is>
+      <c r="B99" s="8" t="n">
+        <v>289</v>
       </c>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
-      <c r="J99" s="8" t="n"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K99" s="8" t="n"/>
-      <c r="L99" s="8" t="n"/>
-      <c r="M99" s="8" t="n"/>
+      <c r="L99" s="8">
+        <f>H99*I99*J99</f>
+        <v/>
+      </c>
+      <c r="M99" s="8" t="n">
+        <v>87</v>
+      </c>
       <c r="N99" s="8">
         <f>L99*3600/M99*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 90</t>
-        </is>
+      <c r="B100" s="9" t="n">
+        <v>290</v>
       </c>
       <c r="C100" s="9" t="n"/>
       <c r="D100" s="9" t="n"/>
       <c r="E100" s="9" t="n"/>
       <c r="F100" s="9" t="n"/>
-      <c r="G100" s="9" t="n"/>
-      <c r="H100" s="9" t="n"/>
-      <c r="I100" s="9" t="n"/>
-      <c r="J100" s="9" t="n"/>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K100" s="9" t="n"/>
-      <c r="L100" s="9" t="n"/>
-      <c r="M100" s="9" t="n"/>
+      <c r="L100" s="8">
+        <f>H100*I100*J100</f>
+        <v/>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>91</v>
+      </c>
       <c r="N100" s="9">
         <f>L100*3600/M100*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 91</t>
-        </is>
+      <c r="B101" s="7" t="n">
+        <v>291</v>
       </c>
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="7" t="n"/>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="7" t="n"/>
-      <c r="I101" s="7" t="n"/>
-      <c r="J101" s="7" t="n"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K101" s="7" t="n"/>
-      <c r="L101" s="7" t="n"/>
-      <c r="M101" s="7" t="n"/>
+      <c r="L101" s="7">
+        <f>H101*I101*J101</f>
+        <v/>
+      </c>
+      <c r="M101" s="7" t="n">
+        <v>28</v>
+      </c>
       <c r="N101" s="7">
         <f>L101*3600/M101*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 92</t>
-        </is>
+      <c r="B102" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="8" t="n"/>
       <c r="E102" s="8" t="n"/>
       <c r="F102" s="8" t="n"/>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="8" t="n"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J102" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K102" s="8" t="n"/>
-      <c r="L102" s="8" t="n"/>
-      <c r="M102" s="8" t="n"/>
+      <c r="L102" s="8">
+        <f>H102*I102*J102</f>
+        <v/>
+      </c>
+      <c r="M102" s="8" t="n">
+        <v>47</v>
+      </c>
       <c r="N102" s="8">
         <f>L102*3600/M102*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 93</t>
-        </is>
+      <c r="B103" s="8" t="n">
+        <v>293</v>
       </c>
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="8" t="n"/>
       <c r="E103" s="8" t="n"/>
       <c r="F103" s="8" t="n"/>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="8" t="n"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I103" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J103" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K103" s="8" t="n"/>
-      <c r="L103" s="8" t="n"/>
-      <c r="M103" s="8" t="n"/>
+      <c r="L103" s="8">
+        <f>H103*I103*J103</f>
+        <v/>
+      </c>
+      <c r="M103" s="8" t="n">
+        <v>29</v>
+      </c>
       <c r="N103" s="8">
         <f>L103*3600/M103*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 94</t>
-        </is>
+      <c r="B104" s="8" t="n">
+        <v>294</v>
       </c>
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="8" t="n"/>
       <c r="E104" s="8" t="n"/>
       <c r="F104" s="8" t="n"/>
-      <c r="G104" s="8" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="8" t="n"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J104" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K104" s="8" t="n"/>
-      <c r="L104" s="8" t="n"/>
-      <c r="M104" s="8" t="n"/>
+      <c r="L104" s="8">
+        <f>H104*I104*J104</f>
+        <v/>
+      </c>
+      <c r="M104" s="8" t="n">
+        <v>72</v>
+      </c>
       <c r="N104" s="8">
         <f>L104*3600/M104*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="105" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 95</t>
-        </is>
+      <c r="B105" s="9" t="n">
+        <v>295</v>
       </c>
       <c r="C105" s="9" t="n"/>
       <c r="D105" s="9" t="n"/>
       <c r="E105" s="9" t="n"/>
       <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="9" t="n"/>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K105" s="9" t="n"/>
-      <c r="L105" s="9" t="n"/>
-      <c r="M105" s="9" t="n"/>
+      <c r="L105" s="8">
+        <f>H105*I105*J105</f>
+        <v/>
+      </c>
+      <c r="M105" s="9" t="n">
+        <v>78</v>
+      </c>
       <c r="N105" s="9">
         <f>L105*3600/M105*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Dozer 96</t>
-        </is>
+      <c r="B106" s="7" t="n">
+        <v>296</v>
       </c>
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="7" t="n"/>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="7" t="n"/>
-      <c r="I106" s="7" t="n"/>
-      <c r="J106" s="7" t="n"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K106" s="7" t="n"/>
-      <c r="L106" s="7" t="n"/>
-      <c r="M106" s="7" t="n"/>
+      <c r="L106" s="7">
+        <f>H106*I106*J106</f>
+        <v/>
+      </c>
+      <c r="M106" s="7" t="n">
+        <v>96</v>
+      </c>
       <c r="N106" s="7">
         <f>L106*3600/M106*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 97</t>
-        </is>
+      <c r="B107" s="8" t="n">
+        <v>297</v>
       </c>
       <c r="C107" s="8" t="n"/>
       <c r="D107" s="8" t="n"/>
       <c r="E107" s="8" t="n"/>
       <c r="F107" s="8" t="n"/>
-      <c r="G107" s="8" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I107" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J107" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K107" s="8" t="n"/>
-      <c r="L107" s="8" t="n"/>
-      <c r="M107" s="8" t="n"/>
+      <c r="L107" s="8">
+        <f>H107*I107*J107</f>
+        <v/>
+      </c>
+      <c r="M107" s="8" t="n">
+        <v>97</v>
+      </c>
       <c r="N107" s="8">
         <f>L107*3600/M107*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 98</t>
-        </is>
+      <c r="B108" s="8" t="n">
+        <v>298</v>
       </c>
       <c r="C108" s="8" t="n"/>
       <c r="D108" s="8" t="n"/>
       <c r="E108" s="8" t="n"/>
       <c r="F108" s="8" t="n"/>
-      <c r="G108" s="8" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I108" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J108" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K108" s="8" t="n"/>
-      <c r="L108" s="8" t="n"/>
-      <c r="M108" s="8" t="n"/>
+      <c r="L108" s="8">
+        <f>H108*I108*J108</f>
+        <v/>
+      </c>
+      <c r="M108" s="8" t="n">
+        <v>94</v>
+      </c>
       <c r="N108" s="8">
         <f>L108*3600/M108*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Dozer 99</t>
-        </is>
+      <c r="B109" s="8" t="n">
+        <v>299</v>
       </c>
       <c r="C109" s="8" t="n"/>
       <c r="D109" s="8" t="n"/>
       <c r="E109" s="8" t="n"/>
       <c r="F109" s="8" t="n"/>
-      <c r="G109" s="8" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-      <c r="J109" s="8" t="n"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I109" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K109" s="8" t="n"/>
-      <c r="L109" s="8" t="n"/>
-      <c r="M109" s="8" t="n"/>
+      <c r="L109" s="8">
+        <f>H109*I109*J109</f>
+        <v/>
+      </c>
+      <c r="M109" s="8" t="n">
+        <v>97</v>
+      </c>
       <c r="N109" s="8">
         <f>L109*3600/M109*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="110" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Dozer 100</t>
-        </is>
+      <c r="B110" s="9" t="n">
+        <v>300</v>
       </c>
       <c r="C110" s="9" t="n"/>
       <c r="D110" s="9" t="n"/>
       <c r="E110" s="9" t="n"/>
       <c r="F110" s="9" t="n"/>
-      <c r="G110" s="9" t="n"/>
-      <c r="H110" s="9" t="n"/>
-      <c r="I110" s="9" t="n"/>
-      <c r="J110" s="9" t="n"/>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>clay and gravel</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I110" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K110" s="9" t="n"/>
-      <c r="L110" s="9" t="n"/>
-      <c r="M110" s="9" t="n"/>
+      <c r="L110" s="8">
+        <f>H110*I110*J110</f>
+        <v/>
+      </c>
+      <c r="M110" s="9" t="n">
+        <v>63</v>
+      </c>
       <c r="N110" s="9">
         <f>L110*3600/M110*0.764555</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="53" t="inlineStr">
+      <c r="B111" s="51" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
@@ -3491,36 +4796,36 @@
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Construction Management Institute </t>
         </is>
       </c>
-      <c r="N1" s="43" t="n"/>
+      <c r="N1" s="49" t="n"/>
     </row>
     <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> PREPARATION OF NATIONAL PRODUCTIVITY NORM FOR WATER CONSTRUCTION TRADE</t>
         </is>
       </c>
-      <c r="N2" s="43" t="n"/>
+      <c r="N2" s="49" t="n"/>
     </row>
     <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">MPDM Data Collection Form </t>
         </is>
       </c>
-      <c r="N3" s="44" t="n"/>
+      <c r="N3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>Form -3</t>
         </is>
       </c>
-      <c r="N4" s="44" t="n"/>
+      <c r="N4" s="50" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" thickBot="1"/>
     <row r="6" ht="27" customHeight="1" thickBot="1">
@@ -3536,7 +4841,7 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="G6" s="52" t="n">
+      <c r="G6" s="46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3554,7 +4859,7 @@
           <t>Unit of Time:</t>
         </is>
       </c>
-      <c r="G8" s="52" t="inlineStr">
+      <c r="G8" s="46" t="inlineStr">
         <is>
           <t>Seconds</t>
         </is>
@@ -3594,10 +4899,10 @@
       <c r="F11" s="59" t="n"/>
       <c r="G11" s="59" t="n"/>
       <c r="H11" s="57" t="n"/>
-      <c r="I11" s="50" t="n"/>
-      <c r="J11" s="50" t="n"/>
-      <c r="K11" s="50" t="n"/>
-      <c r="L11" s="50" t="n"/>
+      <c r="I11" s="44" t="n"/>
+      <c r="J11" s="44" t="n"/>
+      <c r="K11" s="44" t="n"/>
+      <c r="L11" s="44" t="n"/>
       <c r="M11" s="20" t="n"/>
       <c r="O11" s="58" t="inlineStr">
         <is>
@@ -3743,28 +5048,30 @@
       <c r="A13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="55">
+      <c r="B13" s="22" t="n">
+        <v>64</v>
+      </c>
+      <c r="C13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(V13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(W13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(X13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(Y13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="G13" s="55">
+      <c r="G13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(Z13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="40">
         <f>IF(SUM($V13:$AA13), ROUND(AA13/SUM($V13:$AA13), 2),0)</f>
         <v/>
       </c>
@@ -3823,28 +5130,30 @@
       <c r="A14" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="55">
+      <c r="B14" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="C14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(V14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(W14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(X14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(Y14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(Z14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="40">
         <f>IF(SUM($V14:$AA14), ROUND(AA14/SUM($V14:$AA14), 2),0)</f>
         <v/>
       </c>
@@ -3903,28 +5212,30 @@
       <c r="A15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="55">
+      <c r="B15" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="C15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(V15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(W15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(X15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(Y15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="G15" s="55">
+      <c r="G15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(Z15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="40">
         <f>IF(SUM($V15:$AA15), ROUND(AA15/SUM($V15:$AA15), 2),0)</f>
         <v/>
       </c>
@@ -3983,28 +5294,30 @@
       <c r="A16" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="55">
+      <c r="B16" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="C16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(V16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(W16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(X16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(Y16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="G16" s="55">
+      <c r="G16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(Z16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="40">
         <f>IF(SUM($V16:$AA16), ROUND(AA16/SUM($V16:$AA16), 2),0)</f>
         <v/>
       </c>
@@ -4063,28 +5376,30 @@
       <c r="A17" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="55">
+      <c r="B17" s="25" t="n">
+        <v>119</v>
+      </c>
+      <c r="C17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(V17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(W17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(X17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(Y17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="G17" s="55">
+      <c r="G17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(Z17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="40">
         <f>IF(SUM($V17:$AA17), ROUND(AA17/SUM($V17:$AA17), 2),0)</f>
         <v/>
       </c>
@@ -4143,28 +5458,30 @@
       <c r="A18" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="55">
+      <c r="B18" s="25" t="n">
+        <v>83</v>
+      </c>
+      <c r="C18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(V18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(W18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(X18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(Y18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(Z18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="40">
         <f>IF(SUM($V18:$AA18), ROUND(AA18/SUM($V18:$AA18), 2),0)</f>
         <v/>
       </c>
@@ -4223,28 +5540,30 @@
       <c r="A19" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="55">
+      <c r="B19" s="25" t="n">
+        <v>84</v>
+      </c>
+      <c r="C19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(V19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(W19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(X19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(Y19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(Z19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="40">
         <f>IF(SUM($V19:$AA19), ROUND(AA19/SUM($V19:$AA19), 2),0)</f>
         <v/>
       </c>
@@ -4303,28 +5622,30 @@
       <c r="A20" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="55">
+      <c r="B20" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="C20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(V20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(W20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(X20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(Y20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(Z20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="40">
         <f>IF(SUM($V20:$AA20), ROUND(AA20/SUM($V20:$AA20), 2),0)</f>
         <v/>
       </c>
@@ -4383,28 +5704,30 @@
       <c r="A21" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="55">
+      <c r="B21" s="25" t="n">
+        <v>86</v>
+      </c>
+      <c r="C21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(V21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(W21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(X21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(Y21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(Z21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="40">
         <f>IF(SUM($V21:$AA21), ROUND(AA21/SUM($V21:$AA21), 2),0)</f>
         <v/>
       </c>
@@ -4463,28 +5786,30 @@
       <c r="A22" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="55">
+      <c r="B22" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(V22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(W22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(X22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(Y22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(Z22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="40">
         <f>IF(SUM($V22:$AA22), ROUND(AA22/SUM($V22:$AA22), 2),0)</f>
         <v/>
       </c>
@@ -4543,28 +5868,30 @@
       <c r="A23" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="55">
+      <c r="B23" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="C23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(V23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(W23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(X23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(Y23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(Z23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="40">
         <f>IF(SUM($V23:$AA23), ROUND(AA23/SUM($V23:$AA23), 2),0)</f>
         <v/>
       </c>
@@ -4623,28 +5950,30 @@
       <c r="A24" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="55">
+      <c r="B24" s="25" t="n">
+        <v>103</v>
+      </c>
+      <c r="C24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(V24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(W24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(X24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(Y24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(Z24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="40">
         <f>IF(SUM($V24:$AA24), ROUND(AA24/SUM($V24:$AA24), 2),0)</f>
         <v/>
       </c>
@@ -4703,28 +6032,30 @@
       <c r="A25" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="55">
+      <c r="B25" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(V25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(W25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(X25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(Y25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(Z25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="40">
         <f>IF(SUM($V25:$AA25), ROUND(AA25/SUM($V25:$AA25), 2),0)</f>
         <v/>
       </c>
@@ -4783,28 +6114,30 @@
       <c r="A26" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="55">
+      <c r="B26" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="C26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(V26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(W26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(X26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(Y26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(Z26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="40">
         <f>IF(SUM($V26:$AA26), ROUND(AA26/SUM($V26:$AA26), 2),0)</f>
         <v/>
       </c>
@@ -4863,28 +6196,30 @@
       <c r="A27" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="55">
+      <c r="B27" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="C27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(V27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(W27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(X27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(Y27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(Z27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="40">
         <f>IF(SUM($V27:$AA27), ROUND(AA27/SUM($V27:$AA27), 2),0)</f>
         <v/>
       </c>
@@ -4943,28 +6278,30 @@
       <c r="A28" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="55">
+      <c r="B28" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="C28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(V28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(W28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(X28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(Y28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(Z28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
-      <c r="H28" s="55">
+      <c r="H28" s="40">
         <f>IF(SUM($V28:$AA28), ROUND(AA28/SUM($V28:$AA28), 2),0)</f>
         <v/>
       </c>
@@ -5023,28 +6360,30 @@
       <c r="A29" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="55">
+      <c r="B29" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="C29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(V29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(W29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(X29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="F29" s="55">
+      <c r="F29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(Y29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(Z29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
-      <c r="H29" s="55">
+      <c r="H29" s="40">
         <f>IF(SUM($V29:$AA29), ROUND(AA29/SUM($V29:$AA29), 2),0)</f>
         <v/>
       </c>
@@ -5103,28 +6442,30 @@
       <c r="A30" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="55">
+      <c r="B30" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(V30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(W30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(X30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="F30" s="55">
+      <c r="F30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(Y30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(Z30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
-      <c r="H30" s="55">
+      <c r="H30" s="40">
         <f>IF(SUM($V30:$AA30), ROUND(AA30/SUM($V30:$AA30), 2),0)</f>
         <v/>
       </c>
@@ -5183,28 +6524,30 @@
       <c r="A31" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="55">
+      <c r="B31" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="C31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(V31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(W31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(X31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="F31" s="55">
+      <c r="F31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(Y31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(Z31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
-      <c r="H31" s="55">
+      <c r="H31" s="40">
         <f>IF(SUM($V31:$AA31), ROUND(AA31/SUM($V31:$AA31), 2),0)</f>
         <v/>
       </c>
@@ -5263,28 +6606,30 @@
       <c r="A32" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="55">
+      <c r="B32" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(V32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(W32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(X32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="F32" s="55">
+      <c r="F32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(Y32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(Z32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
-      <c r="H32" s="55">
+      <c r="H32" s="40">
         <f>IF(SUM($V32:$AA32), ROUND(AA32/SUM($V32:$AA32), 2),0)</f>
         <v/>
       </c>
@@ -5343,28 +6688,30 @@
       <c r="A33" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="55">
+      <c r="B33" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(V33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="D33" s="55">
+      <c r="D33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(W33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(X33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="F33" s="55">
+      <c r="F33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(Y33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(Z33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
-      <c r="H33" s="55">
+      <c r="H33" s="40">
         <f>IF(SUM($V33:$AA33), ROUND(AA33/SUM($V33:$AA33), 2),0)</f>
         <v/>
       </c>
@@ -5423,28 +6770,30 @@
       <c r="A34" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="55">
+      <c r="B34" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="C34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(V34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(W34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(X34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="F34" s="55">
+      <c r="F34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(Y34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(Z34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
-      <c r="H34" s="55">
+      <c r="H34" s="40">
         <f>IF(SUM($V34:$AA34), ROUND(AA34/SUM($V34:$AA34), 2),0)</f>
         <v/>
       </c>
@@ -5503,28 +6852,30 @@
       <c r="A35" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="55">
+      <c r="B35" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(V35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="D35" s="55">
+      <c r="D35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(W35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(X35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="F35" s="55">
+      <c r="F35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(Y35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(Z35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
-      <c r="H35" s="55">
+      <c r="H35" s="40">
         <f>IF(SUM($V35:$AA35), ROUND(AA35/SUM($V35:$AA35), 2),0)</f>
         <v/>
       </c>
@@ -5583,28 +6934,30 @@
       <c r="A36" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="55">
+      <c r="B36" s="25" t="n">
+        <v>92</v>
+      </c>
+      <c r="C36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(V36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(W36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(X36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="F36" s="55">
+      <c r="F36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(Y36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(Z36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
-      <c r="H36" s="55">
+      <c r="H36" s="40">
         <f>IF(SUM($V36:$AA36), ROUND(AA36/SUM($V36:$AA36), 2),0)</f>
         <v/>
       </c>
@@ -5663,28 +7016,30 @@
       <c r="A37" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="55">
+      <c r="B37" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="C37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(V37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(W37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(X37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(Y37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(Z37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="40">
         <f>IF(SUM($V37:$AA37), ROUND(AA37/SUM($V37:$AA37), 2),0)</f>
         <v/>
       </c>
@@ -5743,28 +7098,30 @@
       <c r="A38" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="55">
+      <c r="B38" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="C38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(V38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(W38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(X38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(Y38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(Z38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
-      <c r="H38" s="55">
+      <c r="H38" s="40">
         <f>IF(SUM($V38:$AA38), ROUND(AA38/SUM($V38:$AA38), 2),0)</f>
         <v/>
       </c>
@@ -5823,28 +7180,30 @@
       <c r="A39" s="21" t="n">
         <v>27</v>
       </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="55">
+      <c r="B39" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="C39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(V39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(W39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(X39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(Y39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(Z39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
-      <c r="H39" s="55">
+      <c r="H39" s="40">
         <f>IF(SUM($V39:$AA39), ROUND(AA39/SUM($V39:$AA39), 2),0)</f>
         <v/>
       </c>
@@ -5903,28 +7262,30 @@
       <c r="A40" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="55">
+      <c r="B40" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(V40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(W40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="E40" s="55">
+      <c r="E40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(X40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="F40" s="55">
+      <c r="F40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(Y40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(Z40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
-      <c r="H40" s="55">
+      <c r="H40" s="40">
         <f>IF(SUM($V40:$AA40), ROUND(AA40/SUM($V40:$AA40), 2),0)</f>
         <v/>
       </c>
@@ -5983,28 +7344,30 @@
       <c r="A41" s="21" t="n">
         <v>29</v>
       </c>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="55">
+      <c r="B41" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="C41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(V41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(W41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="E41" s="55">
+      <c r="E41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(X41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="F41" s="55">
+      <c r="F41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(Y41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(Z41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
-      <c r="H41" s="55">
+      <c r="H41" s="40">
         <f>IF(SUM($V41:$AA41), ROUND(AA41/SUM($V41:$AA41), 2),0)</f>
         <v/>
       </c>
@@ -6063,28 +7426,30 @@
       <c r="A42" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="55">
+      <c r="B42" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="C42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(V42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(W42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="E42" s="55">
+      <c r="E42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(X42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(Y42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(Z42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
-      <c r="H42" s="55">
+      <c r="H42" s="40">
         <f>IF(SUM($V42:$AA42), ROUND(AA42/SUM($V42:$AA42), 2),0)</f>
         <v/>
       </c>
@@ -6143,28 +7508,30 @@
       <c r="A43" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="55">
+      <c r="B43" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="C43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(V43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(W43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="E43" s="55">
+      <c r="E43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(X43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="F43" s="55">
+      <c r="F43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(Y43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="G43" s="55">
+      <c r="G43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(Z43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
-      <c r="H43" s="55">
+      <c r="H43" s="40">
         <f>IF(SUM($V43:$AA43), ROUND(AA43/SUM($V43:$AA43), 2),0)</f>
         <v/>
       </c>
@@ -6223,28 +7590,30 @@
       <c r="A44" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="55">
+      <c r="B44" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(V44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(W44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="E44" s="55">
+      <c r="E44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(X44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(Y44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="G44" s="55">
+      <c r="G44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(Z44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
-      <c r="H44" s="55">
+      <c r="H44" s="40">
         <f>IF(SUM($V44:$AA44), ROUND(AA44/SUM($V44:$AA44), 2),0)</f>
         <v/>
       </c>
@@ -6303,28 +7672,30 @@
       <c r="A45" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="55">
+      <c r="B45" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="C45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(V45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="D45" s="55">
+      <c r="D45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(W45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="E45" s="55">
+      <c r="E45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(X45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="F45" s="55">
+      <c r="F45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(Y45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="G45" s="55">
+      <c r="G45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(Z45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
-      <c r="H45" s="55">
+      <c r="H45" s="40">
         <f>IF(SUM($V45:$AA45), ROUND(AA45/SUM($V45:$AA45), 2),0)</f>
         <v/>
       </c>
@@ -6383,28 +7754,30 @@
       <c r="A46" s="21" t="n">
         <v>34</v>
       </c>
-      <c r="B46" s="25" t="n"/>
-      <c r="C46" s="55">
+      <c r="B46" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(V46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="D46" s="55">
+      <c r="D46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(W46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="E46" s="55">
+      <c r="E46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(X46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="F46" s="55">
+      <c r="F46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(Y46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="G46" s="55">
+      <c r="G46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(Z46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
-      <c r="H46" s="55">
+      <c r="H46" s="40">
         <f>IF(SUM($V46:$AA46), ROUND(AA46/SUM($V46:$AA46), 2),0)</f>
         <v/>
       </c>
@@ -6463,28 +7836,30 @@
       <c r="A47" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="B47" s="25" t="n"/>
-      <c r="C47" s="55">
+      <c r="B47" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="C47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(V47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="D47" s="55">
+      <c r="D47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(W47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="E47" s="55">
+      <c r="E47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(X47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="F47" s="55">
+      <c r="F47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(Y47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="G47" s="55">
+      <c r="G47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(Z47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
-      <c r="H47" s="55">
+      <c r="H47" s="40">
         <f>IF(SUM($V47:$AA47), ROUND(AA47/SUM($V47:$AA47), 2),0)</f>
         <v/>
       </c>
@@ -6543,28 +7918,30 @@
       <c r="A48" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="55">
+      <c r="B48" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(V48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="D48" s="55">
+      <c r="D48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(W48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="E48" s="55">
+      <c r="E48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(X48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="F48" s="55">
+      <c r="F48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(Y48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(Z48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
-      <c r="H48" s="55">
+      <c r="H48" s="40">
         <f>IF(SUM($V48:$AA48), ROUND(AA48/SUM($V48:$AA48), 2),0)</f>
         <v/>
       </c>
@@ -6623,28 +8000,30 @@
       <c r="A49" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="55">
+      <c r="B49" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(V49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="D49" s="55">
+      <c r="D49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(W49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="E49" s="55">
+      <c r="E49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(X49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="F49" s="55">
+      <c r="F49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(Y49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(Z49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
-      <c r="H49" s="55">
+      <c r="H49" s="40">
         <f>IF(SUM($V49:$AA49), ROUND(AA49/SUM($V49:$AA49), 2),0)</f>
         <v/>
       </c>
@@ -6703,28 +8082,30 @@
       <c r="A50" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="B50" s="25" t="n"/>
-      <c r="C50" s="55">
+      <c r="B50" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="C50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(V50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="D50" s="55">
+      <c r="D50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(W50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="E50" s="55">
+      <c r="E50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(X50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="F50" s="55">
+      <c r="F50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(Y50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="G50" s="55">
+      <c r="G50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(Z50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
-      <c r="H50" s="55">
+      <c r="H50" s="40">
         <f>IF(SUM($V50:$AA50), ROUND(AA50/SUM($V50:$AA50), 2),0)</f>
         <v/>
       </c>
@@ -6783,28 +8164,30 @@
       <c r="A51" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="B51" s="25" t="n"/>
-      <c r="C51" s="55">
+      <c r="B51" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(V51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(W51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="E51" s="55">
+      <c r="E51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(X51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="F51" s="55">
+      <c r="F51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(Y51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(Z51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
-      <c r="H51" s="55">
+      <c r="H51" s="40">
         <f>IF(SUM($V51:$AA51), ROUND(AA51/SUM($V51:$AA51), 2),0)</f>
         <v/>
       </c>
@@ -6863,28 +8246,30 @@
       <c r="A52" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="B52" s="25" t="n"/>
-      <c r="C52" s="55">
+      <c r="B52" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="C52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(V52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(W52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="E52" s="55">
+      <c r="E52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(X52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="F52" s="55">
+      <c r="F52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(Y52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(Z52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
-      <c r="H52" s="55">
+      <c r="H52" s="40">
         <f>IF(SUM($V52:$AA52), ROUND(AA52/SUM($V52:$AA52), 2),0)</f>
         <v/>
       </c>
@@ -6943,28 +8328,30 @@
       <c r="A53" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="B53" s="25" t="n"/>
-      <c r="C53" s="55">
+      <c r="B53" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="C53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(V53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="D53" s="55">
+      <c r="D53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(W53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="E53" s="55">
+      <c r="E53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(X53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="F53" s="55">
+      <c r="F53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(Y53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="G53" s="55">
+      <c r="G53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(Z53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
-      <c r="H53" s="55">
+      <c r="H53" s="40">
         <f>IF(SUM($V53:$AA53), ROUND(AA53/SUM($V53:$AA53), 2),0)</f>
         <v/>
       </c>
@@ -7023,28 +8410,30 @@
       <c r="A54" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="55">
+      <c r="B54" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="C54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(V54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="D54" s="55">
+      <c r="D54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(W54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="E54" s="55">
+      <c r="E54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(X54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="F54" s="55">
+      <c r="F54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(Y54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="G54" s="55">
+      <c r="G54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(Z54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
-      <c r="H54" s="55">
+      <c r="H54" s="40">
         <f>IF(SUM($V54:$AA54), ROUND(AA54/SUM($V54:$AA54), 2),0)</f>
         <v/>
       </c>
@@ -7103,28 +8492,30 @@
       <c r="A55" s="21" t="n">
         <v>43</v>
       </c>
-      <c r="B55" s="25" t="n"/>
-      <c r="C55" s="55">
+      <c r="B55" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="C55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(V55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="D55" s="55">
+      <c r="D55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(W55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="E55" s="55">
+      <c r="E55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(X55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="F55" s="55">
+      <c r="F55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(Y55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="G55" s="55">
+      <c r="G55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(Z55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
-      <c r="H55" s="55">
+      <c r="H55" s="40">
         <f>IF(SUM($V55:$AA55), ROUND(AA55/SUM($V55:$AA55), 2),0)</f>
         <v/>
       </c>
@@ -7183,28 +8574,30 @@
       <c r="A56" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="B56" s="25" t="n"/>
-      <c r="C56" s="55">
+      <c r="B56" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="C56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(V56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="D56" s="55">
+      <c r="D56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(W56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="E56" s="55">
+      <c r="E56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(X56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="F56" s="55">
+      <c r="F56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(Y56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="G56" s="55">
+      <c r="G56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(Z56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
-      <c r="H56" s="55">
+      <c r="H56" s="40">
         <f>IF(SUM($V56:$AA56), ROUND(AA56/SUM($V56:$AA56), 2),0)</f>
         <v/>
       </c>
@@ -7263,28 +8656,30 @@
       <c r="A57" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="B57" s="25" t="n"/>
-      <c r="C57" s="55">
+      <c r="B57" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="C57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(V57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="D57" s="55">
+      <c r="D57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(W57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="E57" s="55">
+      <c r="E57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(X57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="F57" s="55">
+      <c r="F57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(Y57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="G57" s="55">
+      <c r="G57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(Z57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
-      <c r="H57" s="55">
+      <c r="H57" s="40">
         <f>IF(SUM($V57:$AA57), ROUND(AA57/SUM($V57:$AA57), 2),0)</f>
         <v/>
       </c>
@@ -7343,28 +8738,30 @@
       <c r="A58" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="B58" s="25" t="n"/>
-      <c r="C58" s="55">
+      <c r="B58" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="C58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(V58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="D58" s="55">
+      <c r="D58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(W58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="E58" s="55">
+      <c r="E58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(X58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="F58" s="55">
+      <c r="F58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(Y58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="G58" s="55">
+      <c r="G58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(Z58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
-      <c r="H58" s="55">
+      <c r="H58" s="40">
         <f>IF(SUM($V58:$AA58), ROUND(AA58/SUM($V58:$AA58), 2),0)</f>
         <v/>
       </c>
@@ -7423,28 +8820,30 @@
       <c r="A59" s="21" t="n">
         <v>47</v>
       </c>
-      <c r="B59" s="25" t="n"/>
-      <c r="C59" s="55">
+      <c r="B59" s="25" t="n">
+        <v>52</v>
+      </c>
+      <c r="C59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(V59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="D59" s="55">
+      <c r="D59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(W59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="E59" s="55">
+      <c r="E59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(X59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="F59" s="55">
+      <c r="F59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(Y59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="G59" s="55">
+      <c r="G59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(Z59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
-      <c r="H59" s="55">
+      <c r="H59" s="40">
         <f>IF(SUM($V59:$AA59), ROUND(AA59/SUM($V59:$AA59), 2),0)</f>
         <v/>
       </c>
@@ -7503,28 +8902,30 @@
       <c r="A60" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="B60" s="25" t="n"/>
-      <c r="C60" s="55">
+      <c r="B60" s="25" t="n">
+        <v>98</v>
+      </c>
+      <c r="C60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(V60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="D60" s="55">
+      <c r="D60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(W60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="E60" s="55">
+      <c r="E60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(X60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="F60" s="55">
+      <c r="F60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(Y60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="G60" s="55">
+      <c r="G60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(Z60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
-      <c r="H60" s="55">
+      <c r="H60" s="40">
         <f>IF(SUM($V60:$AA60), ROUND(AA60/SUM($V60:$AA60), 2),0)</f>
         <v/>
       </c>
@@ -7583,28 +8984,30 @@
       <c r="A61" s="21" t="n">
         <v>49</v>
       </c>
-      <c r="B61" s="25" t="n"/>
-      <c r="C61" s="55">
+      <c r="B61" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(V61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="D61" s="55">
+      <c r="D61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(W61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="E61" s="55">
+      <c r="E61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(X61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(Y61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="G61" s="55">
+      <c r="G61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(Z61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
-      <c r="H61" s="55">
+      <c r="H61" s="40">
         <f>IF(SUM($V61:$AA61), ROUND(AA61/SUM($V61:$AA61), 2),0)</f>
         <v/>
       </c>
@@ -7663,28 +9066,30 @@
       <c r="A62" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="B62" s="25" t="n"/>
-      <c r="C62" s="55">
+      <c r="B62" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="C62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(V62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="D62" s="55">
+      <c r="D62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(W62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="E62" s="55">
+      <c r="E62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(X62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="F62" s="55">
+      <c r="F62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(Y62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="G62" s="55">
+      <c r="G62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(Z62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
-      <c r="H62" s="55">
+      <c r="H62" s="40">
         <f>IF(SUM($V62:$AA62), ROUND(AA62/SUM($V62:$AA62), 2),0)</f>
         <v/>
       </c>
@@ -7743,28 +9148,30 @@
       <c r="A63" s="21" t="n">
         <v>51</v>
       </c>
-      <c r="B63" s="25" t="n"/>
-      <c r="C63" s="55">
+      <c r="B63" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="C63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(V63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="D63" s="55">
+      <c r="D63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(W63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="E63" s="55">
+      <c r="E63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(X63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="F63" s="55">
+      <c r="F63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(Y63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="G63" s="55">
+      <c r="G63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(Z63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
-      <c r="H63" s="55">
+      <c r="H63" s="40">
         <f>IF(SUM($V63:$AA63), ROUND(AA63/SUM($V63:$AA63), 2),0)</f>
         <v/>
       </c>
@@ -7823,28 +9230,30 @@
       <c r="A64" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="B64" s="25" t="n"/>
-      <c r="C64" s="55">
+      <c r="B64" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="C64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(V64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="D64" s="55">
+      <c r="D64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(W64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="E64" s="55">
+      <c r="E64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(X64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="F64" s="55">
+      <c r="F64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(Y64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="G64" s="55">
+      <c r="G64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(Z64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
-      <c r="H64" s="55">
+      <c r="H64" s="40">
         <f>IF(SUM($V64:$AA64), ROUND(AA64/SUM($V64:$AA64), 2),0)</f>
         <v/>
       </c>
@@ -7903,28 +9312,30 @@
       <c r="A65" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="B65" s="25" t="n"/>
-      <c r="C65" s="55">
+      <c r="B65" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(V65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="D65" s="55">
+      <c r="D65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(W65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="E65" s="55">
+      <c r="E65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(X65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="F65" s="55">
+      <c r="F65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(Y65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="G65" s="55">
+      <c r="G65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(Z65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
-      <c r="H65" s="55">
+      <c r="H65" s="40">
         <f>IF(SUM($V65:$AA65), ROUND(AA65/SUM($V65:$AA65), 2),0)</f>
         <v/>
       </c>
@@ -7983,28 +9394,30 @@
       <c r="A66" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="B66" s="25" t="n"/>
-      <c r="C66" s="55">
+      <c r="B66" s="25" t="n">
+        <v>79</v>
+      </c>
+      <c r="C66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(V66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="D66" s="55">
+      <c r="D66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(W66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="E66" s="55">
+      <c r="E66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(X66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="F66" s="55">
+      <c r="F66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(Y66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="G66" s="55">
+      <c r="G66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(Z66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
-      <c r="H66" s="55">
+      <c r="H66" s="40">
         <f>IF(SUM($V66:$AA66), ROUND(AA66/SUM($V66:$AA66), 2),0)</f>
         <v/>
       </c>
@@ -8063,28 +9476,30 @@
       <c r="A67" s="21" t="n">
         <v>55</v>
       </c>
-      <c r="B67" s="25" t="n"/>
-      <c r="C67" s="55">
+      <c r="B67" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="C67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(V67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="D67" s="55">
+      <c r="D67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(W67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="E67" s="55">
+      <c r="E67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(X67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="F67" s="55">
+      <c r="F67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(Y67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="G67" s="55">
+      <c r="G67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(Z67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
-      <c r="H67" s="55">
+      <c r="H67" s="40">
         <f>IF(SUM($V67:$AA67), ROUND(AA67/SUM($V67:$AA67), 2),0)</f>
         <v/>
       </c>
@@ -8143,28 +9558,30 @@
       <c r="A68" s="21" t="n">
         <v>56</v>
       </c>
-      <c r="B68" s="25" t="n"/>
-      <c r="C68" s="55">
+      <c r="B68" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="C68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(V68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="D68" s="55">
+      <c r="D68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(W68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="E68" s="55">
+      <c r="E68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(X68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="F68" s="55">
+      <c r="F68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(Y68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="G68" s="55">
+      <c r="G68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(Z68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
-      <c r="H68" s="55">
+      <c r="H68" s="40">
         <f>IF(SUM($V68:$AA68), ROUND(AA68/SUM($V68:$AA68), 2),0)</f>
         <v/>
       </c>
@@ -8223,28 +9640,30 @@
       <c r="A69" s="21" t="n">
         <v>57</v>
       </c>
-      <c r="B69" s="25" t="n"/>
-      <c r="C69" s="55">
+      <c r="B69" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="C69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(V69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="D69" s="55">
+      <c r="D69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(W69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="E69" s="55">
+      <c r="E69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(X69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="F69" s="55">
+      <c r="F69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(Y69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="G69" s="55">
+      <c r="G69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(Z69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
-      <c r="H69" s="55">
+      <c r="H69" s="40">
         <f>IF(SUM($V69:$AA69), ROUND(AA69/SUM($V69:$AA69), 2),0)</f>
         <v/>
       </c>
@@ -8303,28 +9722,30 @@
       <c r="A70" s="21" t="n">
         <v>58</v>
       </c>
-      <c r="B70" s="25" t="n"/>
-      <c r="C70" s="55">
+      <c r="B70" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(V70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="D70" s="55">
+      <c r="D70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(W70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="E70" s="55">
+      <c r="E70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(X70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="F70" s="55">
+      <c r="F70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(Y70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="G70" s="55">
+      <c r="G70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(Z70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
-      <c r="H70" s="55">
+      <c r="H70" s="40">
         <f>IF(SUM($V70:$AA70), ROUND(AA70/SUM($V70:$AA70), 2),0)</f>
         <v/>
       </c>
@@ -8383,28 +9804,30 @@
       <c r="A71" s="21" t="n">
         <v>59</v>
       </c>
-      <c r="B71" s="25" t="n"/>
-      <c r="C71" s="55">
+      <c r="B71" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="C71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(V71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="D71" s="55">
+      <c r="D71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(W71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="E71" s="55">
+      <c r="E71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(X71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="F71" s="55">
+      <c r="F71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(Y71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="G71" s="55">
+      <c r="G71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(Z71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
-      <c r="H71" s="55">
+      <c r="H71" s="40">
         <f>IF(SUM($V71:$AA71), ROUND(AA71/SUM($V71:$AA71), 2),0)</f>
         <v/>
       </c>
@@ -8463,28 +9886,30 @@
       <c r="A72" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="B72" s="25" t="n"/>
-      <c r="C72" s="55">
+      <c r="B72" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="C72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(V72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="D72" s="55">
+      <c r="D72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(W72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="E72" s="55">
+      <c r="E72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(X72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="F72" s="55">
+      <c r="F72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(Y72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="G72" s="55">
+      <c r="G72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(Z72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
-      <c r="H72" s="55">
+      <c r="H72" s="40">
         <f>IF(SUM($V72:$AA72), ROUND(AA72/SUM($V72:$AA72), 2),0)</f>
         <v/>
       </c>
@@ -8543,28 +9968,30 @@
       <c r="A73" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="B73" s="25" t="n"/>
-      <c r="C73" s="55">
+      <c r="B73" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="C73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(V73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="D73" s="55">
+      <c r="D73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(W73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="E73" s="55">
+      <c r="E73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(X73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="F73" s="55">
+      <c r="F73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(Y73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="G73" s="55">
+      <c r="G73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(Z73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
-      <c r="H73" s="55">
+      <c r="H73" s="40">
         <f>IF(SUM($V73:$AA73), ROUND(AA73/SUM($V73:$AA73), 2),0)</f>
         <v/>
       </c>
@@ -8623,28 +10050,30 @@
       <c r="A74" s="21" t="n">
         <v>62</v>
       </c>
-      <c r="B74" s="25" t="n"/>
-      <c r="C74" s="55">
+      <c r="B74" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(V74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="D74" s="55">
+      <c r="D74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(W74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="E74" s="55">
+      <c r="E74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(X74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="F74" s="55">
+      <c r="F74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(Y74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="G74" s="55">
+      <c r="G74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(Z74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
-      <c r="H74" s="55">
+      <c r="H74" s="40">
         <f>IF(SUM($V74:$AA74), ROUND(AA74/SUM($V74:$AA74), 2),0)</f>
         <v/>
       </c>
@@ -8703,28 +10132,30 @@
       <c r="A75" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="B75" s="25" t="n"/>
-      <c r="C75" s="55">
+      <c r="B75" s="25" t="n">
+        <v>84</v>
+      </c>
+      <c r="C75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(V75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="D75" s="55">
+      <c r="D75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(W75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="E75" s="55">
+      <c r="E75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(X75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="F75" s="55">
+      <c r="F75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(Y75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="G75" s="55">
+      <c r="G75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(Z75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
-      <c r="H75" s="55">
+      <c r="H75" s="40">
         <f>IF(SUM($V75:$AA75), ROUND(AA75/SUM($V75:$AA75), 2),0)</f>
         <v/>
       </c>
@@ -8783,28 +10214,30 @@
       <c r="A76" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="B76" s="25" t="n"/>
-      <c r="C76" s="55">
+      <c r="B76" s="25" t="n">
+        <v>88</v>
+      </c>
+      <c r="C76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(V76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="D76" s="55">
+      <c r="D76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(W76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="E76" s="55">
+      <c r="E76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(X76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="F76" s="55">
+      <c r="F76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(Y76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="G76" s="55">
+      <c r="G76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(Z76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
-      <c r="H76" s="55">
+      <c r="H76" s="40">
         <f>IF(SUM($V76:$AA76), ROUND(AA76/SUM($V76:$AA76), 2),0)</f>
         <v/>
       </c>
@@ -8863,28 +10296,30 @@
       <c r="A77" s="21" t="n">
         <v>65</v>
       </c>
-      <c r="B77" s="25" t="n"/>
-      <c r="C77" s="55">
+      <c r="B77" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="C77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(V77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="D77" s="55">
+      <c r="D77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(W77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="E77" s="55">
+      <c r="E77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(X77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="F77" s="55">
+      <c r="F77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(Y77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="G77" s="55">
+      <c r="G77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(Z77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
-      <c r="H77" s="55">
+      <c r="H77" s="40">
         <f>IF(SUM($V77:$AA77), ROUND(AA77/SUM($V77:$AA77), 2),0)</f>
         <v/>
       </c>
@@ -8943,28 +10378,30 @@
       <c r="A78" s="21" t="n">
         <v>66</v>
       </c>
-      <c r="B78" s="25" t="n"/>
-      <c r="C78" s="55">
+      <c r="B78" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="C78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(V78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="D78" s="55">
+      <c r="D78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(W78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="E78" s="55">
+      <c r="E78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(X78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="F78" s="55">
+      <c r="F78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(Y78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="G78" s="55">
+      <c r="G78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(Z78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
-      <c r="H78" s="55">
+      <c r="H78" s="40">
         <f>IF(SUM($V78:$AA78), ROUND(AA78/SUM($V78:$AA78), 2),0)</f>
         <v/>
       </c>
@@ -9023,28 +10460,30 @@
       <c r="A79" s="21" t="n">
         <v>67</v>
       </c>
-      <c r="B79" s="25" t="n"/>
-      <c r="C79" s="55">
+      <c r="B79" s="25" t="n">
+        <v>109</v>
+      </c>
+      <c r="C79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(V79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="D79" s="55">
+      <c r="D79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(W79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="E79" s="55">
+      <c r="E79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(X79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="F79" s="55">
+      <c r="F79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(Y79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="G79" s="55">
+      <c r="G79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(Z79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
-      <c r="H79" s="55">
+      <c r="H79" s="40">
         <f>IF(SUM($V79:$AA79), ROUND(AA79/SUM($V79:$AA79), 2),0)</f>
         <v/>
       </c>
@@ -9103,28 +10542,30 @@
       <c r="A80" s="21" t="n">
         <v>68</v>
       </c>
-      <c r="B80" s="25" t="n"/>
-      <c r="C80" s="55">
+      <c r="B80" s="25" t="n">
+        <v>112</v>
+      </c>
+      <c r="C80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(V80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="D80" s="55">
+      <c r="D80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(W80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="E80" s="55">
+      <c r="E80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(X80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="F80" s="55">
+      <c r="F80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(Y80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="G80" s="55">
+      <c r="G80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(Z80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
-      <c r="H80" s="55">
+      <c r="H80" s="40">
         <f>IF(SUM($V80:$AA80), ROUND(AA80/SUM($V80:$AA80), 2),0)</f>
         <v/>
       </c>
@@ -9183,28 +10624,30 @@
       <c r="A81" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="B81" s="25" t="n"/>
-      <c r="C81" s="55">
+      <c r="B81" s="25" t="n">
+        <v>107</v>
+      </c>
+      <c r="C81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(V81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="D81" s="55">
+      <c r="D81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(W81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="E81" s="55">
+      <c r="E81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(X81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="F81" s="55">
+      <c r="F81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(Y81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="G81" s="55">
+      <c r="G81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(Z81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
-      <c r="H81" s="55">
+      <c r="H81" s="40">
         <f>IF(SUM($V81:$AA81), ROUND(AA81/SUM($V81:$AA81), 2),0)</f>
         <v/>
       </c>
@@ -9263,28 +10706,30 @@
       <c r="A82" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="B82" s="25" t="n"/>
-      <c r="C82" s="55">
+      <c r="B82" s="25" t="n">
+        <v>108</v>
+      </c>
+      <c r="C82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(V82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="D82" s="55">
+      <c r="D82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(W82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="E82" s="55">
+      <c r="E82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(X82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="F82" s="55">
+      <c r="F82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(Y82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="G82" s="55">
+      <c r="G82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(Z82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
-      <c r="H82" s="55">
+      <c r="H82" s="40">
         <f>IF(SUM($V82:$AA82), ROUND(AA82/SUM($V82:$AA82), 2),0)</f>
         <v/>
       </c>
@@ -9343,28 +10788,30 @@
       <c r="A83" s="21" t="n">
         <v>71</v>
       </c>
-      <c r="B83" s="25" t="n"/>
-      <c r="C83" s="55">
+      <c r="B83" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(V83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="D83" s="55">
+      <c r="D83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(W83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="E83" s="55">
+      <c r="E83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(X83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="F83" s="55">
+      <c r="F83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(Y83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="G83" s="55">
+      <c r="G83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(Z83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
-      <c r="H83" s="55">
+      <c r="H83" s="40">
         <f>IF(SUM($V83:$AA83), ROUND(AA83/SUM($V83:$AA83), 2),0)</f>
         <v/>
       </c>
@@ -9423,28 +10870,30 @@
       <c r="A84" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="B84" s="25" t="n"/>
-      <c r="C84" s="55">
+      <c r="B84" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(V84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="D84" s="55">
+      <c r="D84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(W84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="E84" s="55">
+      <c r="E84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(X84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="F84" s="55">
+      <c r="F84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(Y84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="G84" s="55">
+      <c r="G84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(Z84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
-      <c r="H84" s="55">
+      <c r="H84" s="40">
         <f>IF(SUM($V84:$AA84), ROUND(AA84/SUM($V84:$AA84), 2),0)</f>
         <v/>
       </c>
@@ -9503,28 +10952,30 @@
       <c r="A85" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="B85" s="25" t="n"/>
-      <c r="C85" s="55">
+      <c r="B85" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(V85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="D85" s="55">
+      <c r="D85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(W85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="E85" s="55">
+      <c r="E85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(X85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="F85" s="55">
+      <c r="F85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(Y85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="G85" s="55">
+      <c r="G85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(Z85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
-      <c r="H85" s="55">
+      <c r="H85" s="40">
         <f>IF(SUM($V85:$AA85), ROUND(AA85/SUM($V85:$AA85), 2),0)</f>
         <v/>
       </c>
@@ -9583,28 +11034,30 @@
       <c r="A86" s="21" t="n">
         <v>74</v>
       </c>
-      <c r="B86" s="25" t="n"/>
-      <c r="C86" s="55">
+      <c r="B86" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="C86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(V86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="D86" s="55">
+      <c r="D86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(W86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="E86" s="55">
+      <c r="E86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(X86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="F86" s="55">
+      <c r="F86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(Y86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="G86" s="55">
+      <c r="G86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(Z86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
-      <c r="H86" s="55">
+      <c r="H86" s="40">
         <f>IF(SUM($V86:$AA86), ROUND(AA86/SUM($V86:$AA86), 2),0)</f>
         <v/>
       </c>
@@ -9663,28 +11116,30 @@
       <c r="A87" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="B87" s="25" t="n"/>
-      <c r="C87" s="55">
+      <c r="B87" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="C87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(V87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="D87" s="55">
+      <c r="D87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(W87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="E87" s="55">
+      <c r="E87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(X87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="F87" s="55">
+      <c r="F87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(Y87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="G87" s="55">
+      <c r="G87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(Z87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
-      <c r="H87" s="55">
+      <c r="H87" s="40">
         <f>IF(SUM($V87:$AA87), ROUND(AA87/SUM($V87:$AA87), 2),0)</f>
         <v/>
       </c>
@@ -9743,28 +11198,30 @@
       <c r="A88" s="21" t="n">
         <v>76</v>
       </c>
-      <c r="B88" s="25" t="n"/>
-      <c r="C88" s="55">
+      <c r="B88" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(V88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="D88" s="55">
+      <c r="D88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(W88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="E88" s="55">
+      <c r="E88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(X88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="F88" s="55">
+      <c r="F88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(Y88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="G88" s="55">
+      <c r="G88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(Z88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
-      <c r="H88" s="55">
+      <c r="H88" s="40">
         <f>IF(SUM($V88:$AA88), ROUND(AA88/SUM($V88:$AA88), 2),0)</f>
         <v/>
       </c>
@@ -9823,28 +11280,30 @@
       <c r="A89" s="21" t="n">
         <v>77</v>
       </c>
-      <c r="B89" s="25" t="n"/>
-      <c r="C89" s="55">
+      <c r="B89" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="C89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(V89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="D89" s="55">
+      <c r="D89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(W89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="E89" s="55">
+      <c r="E89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(X89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="F89" s="55">
+      <c r="F89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(Y89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="G89" s="55">
+      <c r="G89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(Z89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
-      <c r="H89" s="55">
+      <c r="H89" s="40">
         <f>IF(SUM($V89:$AA89), ROUND(AA89/SUM($V89:$AA89), 2),0)</f>
         <v/>
       </c>
@@ -9903,28 +11362,30 @@
       <c r="A90" s="21" t="n">
         <v>78</v>
       </c>
-      <c r="B90" s="25" t="n"/>
-      <c r="C90" s="55">
+      <c r="B90" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(V90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="D90" s="55">
+      <c r="D90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(W90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="E90" s="55">
+      <c r="E90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(X90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="F90" s="55">
+      <c r="F90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(Y90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="G90" s="55">
+      <c r="G90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(Z90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
-      <c r="H90" s="55">
+      <c r="H90" s="40">
         <f>IF(SUM($V90:$AA90), ROUND(AA90/SUM($V90:$AA90), 2),0)</f>
         <v/>
       </c>
@@ -9983,28 +11444,30 @@
       <c r="A91" s="21" t="n">
         <v>79</v>
       </c>
-      <c r="B91" s="25" t="n"/>
-      <c r="C91" s="55">
+      <c r="B91" s="25" t="n">
+        <v>98</v>
+      </c>
+      <c r="C91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(V91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="D91" s="55">
+      <c r="D91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(W91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="E91" s="55">
+      <c r="E91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(X91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="F91" s="55">
+      <c r="F91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(Y91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="G91" s="55">
+      <c r="G91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(Z91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
-      <c r="H91" s="55">
+      <c r="H91" s="40">
         <f>IF(SUM($V91:$AA91), ROUND(AA91/SUM($V91:$AA91), 2),0)</f>
         <v/>
       </c>
@@ -10063,28 +11526,30 @@
       <c r="A92" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="55">
+      <c r="B92" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="C92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(V92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="D92" s="55">
+      <c r="D92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(W92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="E92" s="55">
+      <c r="E92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(X92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="F92" s="55">
+      <c r="F92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(Y92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="G92" s="55">
+      <c r="G92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(Z92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
-      <c r="H92" s="55">
+      <c r="H92" s="40">
         <f>IF(SUM($V92:$AA92), ROUND(AA92/SUM($V92:$AA92), 2),0)</f>
         <v/>
       </c>
@@ -10143,28 +11608,30 @@
       <c r="A93" s="21" t="n">
         <v>81</v>
       </c>
-      <c r="B93" s="25" t="n"/>
-      <c r="C93" s="55">
+      <c r="B93" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="C93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(V93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="D93" s="55">
+      <c r="D93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(W93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="E93" s="55">
+      <c r="E93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(X93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="F93" s="55">
+      <c r="F93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(Y93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="G93" s="55">
+      <c r="G93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(Z93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
-      <c r="H93" s="55">
+      <c r="H93" s="40">
         <f>IF(SUM($V93:$AA93), ROUND(AA93/SUM($V93:$AA93), 2),0)</f>
         <v/>
       </c>
@@ -10223,28 +11690,30 @@
       <c r="A94" s="21" t="n">
         <v>82</v>
       </c>
-      <c r="B94" s="25" t="n"/>
-      <c r="C94" s="55">
+      <c r="B94" s="25" t="n">
+        <v>83</v>
+      </c>
+      <c r="C94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(V94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="D94" s="55">
+      <c r="D94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(W94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="E94" s="55">
+      <c r="E94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(X94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="F94" s="55">
+      <c r="F94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(Y94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="G94" s="55">
+      <c r="G94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(Z94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
-      <c r="H94" s="55">
+      <c r="H94" s="40">
         <f>IF(SUM($V94:$AA94), ROUND(AA94/SUM($V94:$AA94), 2),0)</f>
         <v/>
       </c>
@@ -10303,28 +11772,30 @@
       <c r="A95" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="B95" s="25" t="n"/>
-      <c r="C95" s="55">
+      <c r="B95" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="C95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(V95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="D95" s="55">
+      <c r="D95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(W95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="E95" s="55">
+      <c r="E95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(X95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="F95" s="55">
+      <c r="F95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(Y95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="G95" s="55">
+      <c r="G95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(Z95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
-      <c r="H95" s="55">
+      <c r="H95" s="40">
         <f>IF(SUM($V95:$AA95), ROUND(AA95/SUM($V95:$AA95), 2),0)</f>
         <v/>
       </c>
@@ -10383,28 +11854,30 @@
       <c r="A96" s="21" t="n">
         <v>84</v>
       </c>
-      <c r="B96" s="25" t="n"/>
-      <c r="C96" s="55">
+      <c r="B96" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="C96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(V96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="D96" s="55">
+      <c r="D96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(W96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="E96" s="55">
+      <c r="E96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(X96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="F96" s="55">
+      <c r="F96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(Y96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="G96" s="55">
+      <c r="G96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(Z96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
-      <c r="H96" s="55">
+      <c r="H96" s="40">
         <f>IF(SUM($V96:$AA96), ROUND(AA96/SUM($V96:$AA96), 2),0)</f>
         <v/>
       </c>
@@ -10463,28 +11936,30 @@
       <c r="A97" s="21" t="n">
         <v>85</v>
       </c>
-      <c r="B97" s="25" t="n"/>
-      <c r="C97" s="55">
+      <c r="B97" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="C97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(V97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="D97" s="55">
+      <c r="D97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(W97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="E97" s="55">
+      <c r="E97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(X97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="F97" s="55">
+      <c r="F97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(Y97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="G97" s="55">
+      <c r="G97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(Z97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
-      <c r="H97" s="55">
+      <c r="H97" s="40">
         <f>IF(SUM($V97:$AA97), ROUND(AA97/SUM($V97:$AA97), 2),0)</f>
         <v/>
       </c>
@@ -10543,28 +12018,30 @@
       <c r="A98" s="21" t="n">
         <v>86</v>
       </c>
-      <c r="B98" s="25" t="n"/>
-      <c r="C98" s="55">
+      <c r="B98" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="C98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(V98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="D98" s="55">
+      <c r="D98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(W98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="E98" s="55">
+      <c r="E98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(X98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="F98" s="55">
+      <c r="F98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(Y98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="G98" s="55">
+      <c r="G98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(Z98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
-      <c r="H98" s="55">
+      <c r="H98" s="40">
         <f>IF(SUM($V98:$AA98), ROUND(AA98/SUM($V98:$AA98), 2),0)</f>
         <v/>
       </c>
@@ -10623,28 +12100,30 @@
       <c r="A99" s="21" t="n">
         <v>87</v>
       </c>
-      <c r="B99" s="25" t="n"/>
-      <c r="C99" s="55">
+      <c r="B99" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="C99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(V99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="D99" s="55">
+      <c r="D99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(W99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="E99" s="55">
+      <c r="E99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(X99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="F99" s="55">
+      <c r="F99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(Y99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="G99" s="55">
+      <c r="G99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(Z99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
-      <c r="H99" s="55">
+      <c r="H99" s="40">
         <f>IF(SUM($V99:$AA99), ROUND(AA99/SUM($V99:$AA99), 2),0)</f>
         <v/>
       </c>
@@ -10703,28 +12182,30 @@
       <c r="A100" s="21" t="n">
         <v>88</v>
       </c>
-      <c r="B100" s="25" t="n"/>
-      <c r="C100" s="55">
+      <c r="B100" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="C100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(V100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="D100" s="55">
+      <c r="D100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(W100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="E100" s="55">
+      <c r="E100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(X100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="F100" s="55">
+      <c r="F100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(Y100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="G100" s="55">
+      <c r="G100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(Z100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
-      <c r="H100" s="55">
+      <c r="H100" s="40">
         <f>IF(SUM($V100:$AA100), ROUND(AA100/SUM($V100:$AA100), 2),0)</f>
         <v/>
       </c>
@@ -10783,28 +12264,30 @@
       <c r="A101" s="21" t="n">
         <v>89</v>
       </c>
-      <c r="B101" s="25" t="n"/>
-      <c r="C101" s="55">
+      <c r="B101" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="C101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(V101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="D101" s="55">
+      <c r="D101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(W101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="E101" s="55">
+      <c r="E101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(X101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="F101" s="55">
+      <c r="F101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(Y101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="G101" s="55">
+      <c r="G101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(Z101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
-      <c r="H101" s="55">
+      <c r="H101" s="40">
         <f>IF(SUM($V101:$AA101), ROUND(AA101/SUM($V101:$AA101), 2),0)</f>
         <v/>
       </c>
@@ -10863,28 +12346,30 @@
       <c r="A102" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="B102" s="25" t="n"/>
-      <c r="C102" s="55">
+      <c r="B102" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="C102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(V102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="D102" s="55">
+      <c r="D102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(W102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="E102" s="55">
+      <c r="E102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(X102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="F102" s="55">
+      <c r="F102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(Y102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="G102" s="55">
+      <c r="G102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(Z102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
-      <c r="H102" s="55">
+      <c r="H102" s="40">
         <f>IF(SUM($V102:$AA102), ROUND(AA102/SUM($V102:$AA102), 2),0)</f>
         <v/>
       </c>
@@ -10943,28 +12428,30 @@
       <c r="A103" s="21" t="n">
         <v>91</v>
       </c>
-      <c r="B103" s="25" t="n"/>
-      <c r="C103" s="55">
+      <c r="B103" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(V103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="D103" s="55">
+      <c r="D103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(W103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="E103" s="55">
+      <c r="E103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(X103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="F103" s="55">
+      <c r="F103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(Y103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="G103" s="55">
+      <c r="G103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(Z103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
-      <c r="H103" s="55">
+      <c r="H103" s="40">
         <f>IF(SUM($V103:$AA103), ROUND(AA103/SUM($V103:$AA103), 2),0)</f>
         <v/>
       </c>
@@ -11023,28 +12510,30 @@
       <c r="A104" s="21" t="n">
         <v>92</v>
       </c>
-      <c r="B104" s="25" t="n"/>
-      <c r="C104" s="55">
+      <c r="B104" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="C104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(V104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="D104" s="55">
+      <c r="D104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(W104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="E104" s="55">
+      <c r="E104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(X104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="F104" s="55">
+      <c r="F104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(Y104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="G104" s="55">
+      <c r="G104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(Z104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
-      <c r="H104" s="55">
+      <c r="H104" s="40">
         <f>IF(SUM($V104:$AA104), ROUND(AA104/SUM($V104:$AA104), 2),0)</f>
         <v/>
       </c>
@@ -11103,28 +12592,30 @@
       <c r="A105" s="21" t="n">
         <v>93</v>
       </c>
-      <c r="B105" s="25" t="n"/>
-      <c r="C105" s="55">
+      <c r="B105" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="C105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(V105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="D105" s="55">
+      <c r="D105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(W105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="E105" s="55">
+      <c r="E105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(X105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="F105" s="55">
+      <c r="F105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(Y105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="G105" s="55">
+      <c r="G105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(Z105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
-      <c r="H105" s="55">
+      <c r="H105" s="40">
         <f>IF(SUM($V105:$AA105), ROUND(AA105/SUM($V105:$AA105), 2),0)</f>
         <v/>
       </c>
@@ -11183,28 +12674,30 @@
       <c r="A106" s="21" t="n">
         <v>94</v>
       </c>
-      <c r="B106" s="25" t="n"/>
-      <c r="C106" s="55">
+      <c r="B106" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(V106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="D106" s="55">
+      <c r="D106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(W106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="E106" s="55">
+      <c r="E106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(X106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="F106" s="55">
+      <c r="F106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(Y106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="G106" s="55">
+      <c r="G106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(Z106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
-      <c r="H106" s="55">
+      <c r="H106" s="40">
         <f>IF(SUM($V106:$AA106), ROUND(AA106/SUM($V106:$AA106), 2),0)</f>
         <v/>
       </c>
@@ -11263,28 +12756,30 @@
       <c r="A107" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="B107" s="25" t="n"/>
-      <c r="C107" s="55">
+      <c r="B107" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="C107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(V107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="D107" s="55">
+      <c r="D107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(W107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="E107" s="55">
+      <c r="E107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(X107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="F107" s="55">
+      <c r="F107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(Y107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="G107" s="55">
+      <c r="G107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(Z107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
-      <c r="H107" s="55">
+      <c r="H107" s="40">
         <f>IF(SUM($V107:$AA107), ROUND(AA107/SUM($V107:$AA107), 2),0)</f>
         <v/>
       </c>
@@ -11343,28 +12838,30 @@
       <c r="A108" s="21" t="n">
         <v>96</v>
       </c>
-      <c r="B108" s="25" t="n"/>
-      <c r="C108" s="55">
+      <c r="B108" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="C108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(V108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="D108" s="55">
+      <c r="D108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(W108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="E108" s="55">
+      <c r="E108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(X108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="F108" s="55">
+      <c r="F108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(Y108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="G108" s="55">
+      <c r="G108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(Z108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
-      <c r="H108" s="55">
+      <c r="H108" s="40">
         <f>IF(SUM($V108:$AA108), ROUND(AA108/SUM($V108:$AA108), 2),0)</f>
         <v/>
       </c>
@@ -11423,28 +12920,30 @@
       <c r="A109" s="21" t="n">
         <v>97</v>
       </c>
-      <c r="B109" s="25" t="n"/>
-      <c r="C109" s="55">
+      <c r="B109" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="C109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(V109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="D109" s="55">
+      <c r="D109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(W109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="E109" s="55">
+      <c r="E109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(X109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="F109" s="55">
+      <c r="F109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(Y109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="G109" s="55">
+      <c r="G109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(Z109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
-      <c r="H109" s="55">
+      <c r="H109" s="40">
         <f>IF(SUM($V109:$AA109), ROUND(AA109/SUM($V109:$AA109), 2),0)</f>
         <v/>
       </c>
@@ -11503,28 +13002,30 @@
       <c r="A110" s="21" t="n">
         <v>98</v>
       </c>
-      <c r="B110" s="25" t="n"/>
-      <c r="C110" s="55">
+      <c r="B110" s="25" t="n">
+        <v>94</v>
+      </c>
+      <c r="C110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(V110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="D110" s="55">
+      <c r="D110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(W110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="E110" s="55">
+      <c r="E110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(X110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="F110" s="55">
+      <c r="F110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(Y110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="G110" s="55">
+      <c r="G110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(Z110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
-      <c r="H110" s="55">
+      <c r="H110" s="40">
         <f>IF(SUM($V110:$AA110), ROUND(AA110/SUM($V110:$AA110), 2),0)</f>
         <v/>
       </c>
@@ -11583,28 +13084,30 @@
       <c r="A111" s="21" t="n">
         <v>99</v>
       </c>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="55">
+      <c r="B111" s="25" t="n">
+        <v>97</v>
+      </c>
+      <c r="C111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(V111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="D111" s="55">
+      <c r="D111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(W111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="E111" s="55">
+      <c r="E111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(X111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="F111" s="55">
+      <c r="F111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(Y111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="G111" s="55">
+      <c r="G111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(Z111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
-      <c r="H111" s="55">
+      <c r="H111" s="40">
         <f>IF(SUM($V111:$AA111), ROUND(AA111/SUM($V111:$AA111), 2),0)</f>
         <v/>
       </c>
@@ -11663,28 +13166,30 @@
       <c r="A112" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="B112" s="27" t="n"/>
-      <c r="C112" s="56">
+      <c r="B112" s="27" t="n">
+        <v>63</v>
+      </c>
+      <c r="C112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(V112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="D112" s="56">
+      <c r="D112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(W112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="E112" s="56">
+      <c r="E112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(X112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="F112" s="56">
+      <c r="F112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(Y112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="G112" s="56">
+      <c r="G112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(Z112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
-      <c r="H112" s="56">
+      <c r="H112" s="41">
         <f>IF(SUM($V112:$AA112), ROUND(AA112/SUM($V112:$AA112), 2),0)</f>
         <v/>
       </c>
@@ -12125,8 +13630,8 @@
     <mergeCell ref="V11:AA11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A3:M3"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A3:M3"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A2:M2"/>
